--- a/useroutlet.xlsx
+++ b/useroutlet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\INSP-PRAYU\MataLangit\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79755F09-4A2E-4ABA-AC9A-6320170C91C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2F57169-647F-41E8-AAF5-F81E771A2745}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9510" yWindow="0" windowWidth="9780" windowHeight="10170" xr2:uid="{BA2FB3B7-DDB7-4BF1-80F8-0A6743FFEB63}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{BA2FB3B7-DDB7-4BF1-80F8-0A6743FFEB63}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3832" uniqueCount="996">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3838" uniqueCount="996">
   <si>
     <t>Role</t>
   </si>
@@ -5247,7 +5247,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A746E14-DA6E-4106-846A-771E18ABB4AC}">
-  <dimension ref="A1:D996"/>
+  <dimension ref="A1:D998"/>
   <sheetFormatPr defaultColWidth="8.640625" defaultRowHeight="17.5" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="1" max="1" width="8.42578125" bestFit="1" customWidth="1"/>
@@ -19195,6 +19195,34 @@
       </c>
       <c r="D996" t="s">
         <v>113</v>
+      </c>
+    </row>
+    <row r="997" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A997" s="12" t="s">
+        <v>570</v>
+      </c>
+      <c r="B997">
+        <v>2613051349</v>
+      </c>
+      <c r="C997" s="10" t="s">
+        <v>571</v>
+      </c>
+      <c r="D997" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="998" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A998" s="12" t="s">
+        <v>570</v>
+      </c>
+      <c r="B998">
+        <v>2613051179</v>
+      </c>
+      <c r="C998" s="10" t="s">
+        <v>571</v>
+      </c>
+      <c r="D998" t="s">
+        <v>114</v>
       </c>
     </row>
   </sheetData>

--- a/useroutlet.xlsx
+++ b/useroutlet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\INSP-PRAYU\MataLangit\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2F57169-647F-41E8-AAF5-F81E771A2745}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF35F92F-BE11-4C8F-9A4A-5F3F46F59B69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{BA2FB3B7-DDB7-4BF1-80F8-0A6743FFEB63}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3838" uniqueCount="996">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5640" uniqueCount="1430">
   <si>
     <t>Role</t>
   </si>
@@ -3008,37 +3008,1353 @@
     <t>FRONTLINER</t>
   </si>
   <si>
-    <t>FLTEST</t>
-  </si>
-  <si>
-    <t>PROMOTOR</t>
-  </si>
-  <si>
-    <t>PROMTEST</t>
-  </si>
-  <si>
-    <t>FLTEST_IM3</t>
-  </si>
-  <si>
-    <t>PROMTEST_IM3</t>
-  </si>
-  <si>
     <t>DSE324020002</t>
   </si>
   <si>
     <t>1-28825219235</t>
+  </si>
+  <si>
+    <t>AE</t>
+  </si>
+  <si>
+    <t>AECJJAVA0001</t>
+  </si>
+  <si>
+    <t>AECJJAVA0002</t>
+  </si>
+  <si>
+    <t>AECJJAVA0003</t>
+  </si>
+  <si>
+    <t>AECJJAVA0004</t>
+  </si>
+  <si>
+    <t>AECJJAVA0005</t>
+  </si>
+  <si>
+    <t>AECJJAVA0006</t>
+  </si>
+  <si>
+    <t>AECJJAVA0007</t>
+  </si>
+  <si>
+    <t>AECJJAVA0008</t>
+  </si>
+  <si>
+    <t>AECJJAVA0009</t>
+  </si>
+  <si>
+    <t>AECJJAVA0010</t>
+  </si>
+  <si>
+    <t>AECJJAVA0011</t>
+  </si>
+  <si>
+    <t>AECJJAVA0012</t>
+  </si>
+  <si>
+    <t>AECJJAVA0013</t>
+  </si>
+  <si>
+    <t>AECJJAVA0014</t>
+  </si>
+  <si>
+    <t>AECJJAVA0015</t>
+  </si>
+  <si>
+    <t>AECJJAVA0016</t>
+  </si>
+  <si>
+    <t>AECJJAVA0017</t>
+  </si>
+  <si>
+    <t>AECJJAVA0018</t>
+  </si>
+  <si>
+    <t>AECJJAVA0019</t>
+  </si>
+  <si>
+    <t>AECJJAVA0020</t>
+  </si>
+  <si>
+    <t>AECJJAVA0021</t>
+  </si>
+  <si>
+    <t>AECJJAVA0022</t>
+  </si>
+  <si>
+    <t>AECJJAVA0023</t>
+  </si>
+  <si>
+    <t>AECJJAVA0024</t>
+  </si>
+  <si>
+    <t>AECJJAVA0049</t>
+  </si>
+  <si>
+    <t>AECJJAVA0026</t>
+  </si>
+  <si>
+    <t>AECJJAVA0027</t>
+  </si>
+  <si>
+    <t>AECJJAVA0028</t>
+  </si>
+  <si>
+    <t>AECJJAVA0029</t>
+  </si>
+  <si>
+    <t>AECJJAVA0030</t>
+  </si>
+  <si>
+    <t>AECJJAVA0033</t>
+  </si>
+  <si>
+    <t>AECJJAVA0032</t>
+  </si>
+  <si>
+    <t>AECJJAVA0031</t>
+  </si>
+  <si>
+    <t>AECJJAVA0034</t>
+  </si>
+  <si>
+    <t>AECJJAVA0035</t>
+  </si>
+  <si>
+    <t>AECJJAVA0036</t>
+  </si>
+  <si>
+    <t>AECJJAVA0037</t>
+  </si>
+  <si>
+    <t>AECJJAVA0038</t>
+  </si>
+  <si>
+    <t>AECJJAVA0039</t>
+  </si>
+  <si>
+    <t>AECJJAVA0040</t>
+  </si>
+  <si>
+    <t>AECJJAVA0041</t>
+  </si>
+  <si>
+    <t>AECJJAVA0042</t>
+  </si>
+  <si>
+    <t>AECJJAVA0043</t>
+  </si>
+  <si>
+    <t>AECJJAVA0044</t>
+  </si>
+  <si>
+    <t>AECJJAVA0045</t>
+  </si>
+  <si>
+    <t>AECJJAVA0046</t>
+  </si>
+  <si>
+    <t>AECJJAVA0047</t>
+  </si>
+  <si>
+    <t>FL_17188932</t>
+  </si>
+  <si>
+    <t>FL1234!</t>
+  </si>
+  <si>
+    <t>FL_17683884</t>
+  </si>
+  <si>
+    <t>FL_1526108</t>
+  </si>
+  <si>
+    <t>FL_674785</t>
+  </si>
+  <si>
+    <t>FL_586076</t>
+  </si>
+  <si>
+    <t>FL_17158019</t>
+  </si>
+  <si>
+    <t>FL_505646</t>
+  </si>
+  <si>
+    <t>FL_620025</t>
+  </si>
+  <si>
+    <t>FL_1292187</t>
+  </si>
+  <si>
+    <t>FL_17359265</t>
+  </si>
+  <si>
+    <t>FL_514553</t>
+  </si>
+  <si>
+    <t>FL_17700936</t>
+  </si>
+  <si>
+    <t>FL_17078325</t>
+  </si>
+  <si>
+    <t>FL_623322</t>
+  </si>
+  <si>
+    <t>FL_966097</t>
+  </si>
+  <si>
+    <t>FL_17454924</t>
+  </si>
+  <si>
+    <t>FL_17125068</t>
+  </si>
+  <si>
+    <t>FL_17087772</t>
+  </si>
+  <si>
+    <t>FL_17373592</t>
+  </si>
+  <si>
+    <t>FL_17336277</t>
+  </si>
+  <si>
+    <t>FL_17416713</t>
+  </si>
+  <si>
+    <t>FL_17376127</t>
+  </si>
+  <si>
+    <t>FL_17411249</t>
+  </si>
+  <si>
+    <t>FL_17519857</t>
+  </si>
+  <si>
+    <t>FL_17657947</t>
+  </si>
+  <si>
+    <t>FL_1288333</t>
+  </si>
+  <si>
+    <t>FL_00504559</t>
+  </si>
+  <si>
+    <t>FL_00268881</t>
+  </si>
+  <si>
+    <t>FL_00172738</t>
+  </si>
+  <si>
+    <t>FL_00237563</t>
+  </si>
+  <si>
+    <t>FL_00286423</t>
+  </si>
+  <si>
+    <t>FL_00121377</t>
+  </si>
+  <si>
+    <t>FL_00243866</t>
+  </si>
+  <si>
+    <t>FL_00135887</t>
+  </si>
+  <si>
+    <t>FL_00377613</t>
+  </si>
+  <si>
+    <t>FL_00230381</t>
+  </si>
+  <si>
+    <t>FL_00383240</t>
+  </si>
+  <si>
+    <t>FL_00423021</t>
+  </si>
+  <si>
+    <t>FL_00130858</t>
+  </si>
+  <si>
+    <t>FL_00283673</t>
+  </si>
+  <si>
+    <t>FL_00085572</t>
+  </si>
+  <si>
+    <t>FL_00322248</t>
+  </si>
+  <si>
+    <t>FL_00253987</t>
+  </si>
+  <si>
+    <t>FL_00198447</t>
+  </si>
+  <si>
+    <t>FL_00064636</t>
+  </si>
+  <si>
+    <t>FL_00290786</t>
+  </si>
+  <si>
+    <t>FL_00492914</t>
+  </si>
+  <si>
+    <t>FL_00553908</t>
+  </si>
+  <si>
+    <t>FL_00506582</t>
+  </si>
+  <si>
+    <t>FL_00065431</t>
+  </si>
+  <si>
+    <t>FL_00318476</t>
+  </si>
+  <si>
+    <t>FL_00080768</t>
+  </si>
+  <si>
+    <t>FL_00206337</t>
+  </si>
+  <si>
+    <t>FL_00317189</t>
+  </si>
+  <si>
+    <t>FL_00123746</t>
+  </si>
+  <si>
+    <t>FL_00043503</t>
+  </si>
+  <si>
+    <t>FL_00172896</t>
+  </si>
+  <si>
+    <t>FL_00173258</t>
+  </si>
+  <si>
+    <t>FL_00427940</t>
+  </si>
+  <si>
+    <t>FL_17639945</t>
+  </si>
+  <si>
+    <t>FL_1463638</t>
+  </si>
+  <si>
+    <t>FL_678931</t>
+  </si>
+  <si>
+    <t>FL_17179189</t>
+  </si>
+  <si>
+    <t>FL_687459</t>
+  </si>
+  <si>
+    <t>FL_833812</t>
+  </si>
+  <si>
+    <t>FL_17011621</t>
+  </si>
+  <si>
+    <t>FL_17162979</t>
+  </si>
+  <si>
+    <t>FL_00085426</t>
+  </si>
+  <si>
+    <t>FL_00086114</t>
+  </si>
+  <si>
+    <t>FL_00173041</t>
+  </si>
+  <si>
+    <t>FL_00071408</t>
+  </si>
+  <si>
+    <t>FL_00018450</t>
+  </si>
+  <si>
+    <t>FL_17318420</t>
+  </si>
+  <si>
+    <t>FL_834372</t>
+  </si>
+  <si>
+    <t>FL_860478</t>
+  </si>
+  <si>
+    <t>FL_1318274</t>
+  </si>
+  <si>
+    <t>FL_00500838</t>
+  </si>
+  <si>
+    <t>FL_00155374</t>
+  </si>
+  <si>
+    <t>FL_00155097</t>
+  </si>
+  <si>
+    <t>FL_00173197</t>
+  </si>
+  <si>
+    <t>FL_00232938</t>
+  </si>
+  <si>
+    <t>FL_00136102</t>
+  </si>
+  <si>
+    <t>FL_00254424</t>
+  </si>
+  <si>
+    <t>FL_1294896</t>
+  </si>
+  <si>
+    <t>FL_1305701</t>
+  </si>
+  <si>
+    <t>FL_1570292</t>
+  </si>
+  <si>
+    <t>FL_00467601</t>
+  </si>
+  <si>
+    <t>FL_00141820</t>
+  </si>
+  <si>
+    <t>FL_00519842</t>
+  </si>
+  <si>
+    <t>FL_00048149</t>
+  </si>
+  <si>
+    <t>FL_00510077</t>
+  </si>
+  <si>
+    <t>FL_12331574</t>
+  </si>
+  <si>
+    <t>FL_12331786</t>
+  </si>
+  <si>
+    <t>FL_12331480</t>
+  </si>
+  <si>
+    <t>FL_12333594</t>
+  </si>
+  <si>
+    <t>FL_00184439</t>
+  </si>
+  <si>
+    <t>FL_00347908</t>
+  </si>
+  <si>
+    <t>FL_00154458</t>
+  </si>
+  <si>
+    <t>FL_00411511</t>
+  </si>
+  <si>
+    <t>FL_00519798</t>
+  </si>
+  <si>
+    <t>FL_00118871</t>
+  </si>
+  <si>
+    <t>FL_00394869</t>
+  </si>
+  <si>
+    <t>FL_00122380</t>
+  </si>
+  <si>
+    <t>FL_00533660</t>
+  </si>
+  <si>
+    <t>FL_00315588</t>
+  </si>
+  <si>
+    <t>FL_00494218</t>
+  </si>
+  <si>
+    <t>FL_00233498</t>
+  </si>
+  <si>
+    <t>FL_00005561</t>
+  </si>
+  <si>
+    <t>FL_00066538</t>
+  </si>
+  <si>
+    <t>FL_00548995</t>
+  </si>
+  <si>
+    <t>FL_00150393</t>
+  </si>
+  <si>
+    <t>FL_502261</t>
+  </si>
+  <si>
+    <t>FL_17611910</t>
+  </si>
+  <si>
+    <t>FL_1327940</t>
+  </si>
+  <si>
+    <t>FL_607544</t>
+  </si>
+  <si>
+    <t>FL_17467849</t>
+  </si>
+  <si>
+    <t>FL_17713279</t>
+  </si>
+  <si>
+    <t>FL_17138150</t>
+  </si>
+  <si>
+    <t>FL_1549441</t>
+  </si>
+  <si>
+    <t>FL_17168674</t>
+  </si>
+  <si>
+    <t>FL_601212</t>
+  </si>
+  <si>
+    <t>FL_585479</t>
+  </si>
+  <si>
+    <t>FL_1511178</t>
+  </si>
+  <si>
+    <t>FL_17631943</t>
+  </si>
+  <si>
+    <t>FL_17673533</t>
+  </si>
+  <si>
+    <t>FL_17511308</t>
+  </si>
+  <si>
+    <t>FL_1554616</t>
+  </si>
+  <si>
+    <t>FL_1514630</t>
+  </si>
+  <si>
+    <t>FL_17804252</t>
+  </si>
+  <si>
+    <t>FL_1288848</t>
+  </si>
+  <si>
+    <t>FL_1084662</t>
+  </si>
+  <si>
+    <t>FL_17656857</t>
+  </si>
+  <si>
+    <t>FL_736057</t>
+  </si>
+  <si>
+    <t>FL_707386</t>
+  </si>
+  <si>
+    <t>FL_17659216</t>
+  </si>
+  <si>
+    <t>FL_17661481</t>
+  </si>
+  <si>
+    <t>FL_00047950</t>
+  </si>
+  <si>
+    <t>FL_17672078</t>
+  </si>
+  <si>
+    <t>FL_595479</t>
+  </si>
+  <si>
+    <t>FL_00479423</t>
+  </si>
+  <si>
+    <t>FL_830854</t>
+  </si>
+  <si>
+    <t>FL_17125147</t>
+  </si>
+  <si>
+    <t>FL_17233808</t>
+  </si>
+  <si>
+    <t>FL_17123882</t>
+  </si>
+  <si>
+    <t>FL_17301557</t>
+  </si>
+  <si>
+    <t>FL_17158331</t>
+  </si>
+  <si>
+    <t>FL_00080902</t>
+  </si>
+  <si>
+    <t>FL_00099997</t>
+  </si>
+  <si>
+    <t>FL_00141859</t>
+  </si>
+  <si>
+    <t>FL_00198309</t>
+  </si>
+  <si>
+    <t>FL_00382795</t>
+  </si>
+  <si>
+    <t>FL_00295614</t>
+  </si>
+  <si>
+    <t>FL_00496504</t>
+  </si>
+  <si>
+    <t>FL_00244032</t>
+  </si>
+  <si>
+    <t>FL_00163445</t>
+  </si>
+  <si>
+    <t>FL_00341797</t>
+  </si>
+  <si>
+    <t>FL_00059193</t>
+  </si>
+  <si>
+    <t>FL_00088205</t>
+  </si>
+  <si>
+    <t>FL_00330000</t>
+  </si>
+  <si>
+    <t>FL_00059178</t>
+  </si>
+  <si>
+    <t>FL_00246846</t>
+  </si>
+  <si>
+    <t>FL_00293768</t>
+  </si>
+  <si>
+    <t>FL_00498095</t>
+  </si>
+  <si>
+    <t>FL_00042687</t>
+  </si>
+  <si>
+    <t>FL_00206106</t>
+  </si>
+  <si>
+    <t>FL_00434055</t>
+  </si>
+  <si>
+    <t>FL_00296056</t>
+  </si>
+  <si>
+    <t>FL_00246756</t>
+  </si>
+  <si>
+    <t>FL_00121098</t>
+  </si>
+  <si>
+    <t>FL_00014008</t>
+  </si>
+  <si>
+    <t>FL_00162714</t>
+  </si>
+  <si>
+    <t>FL_00085733</t>
+  </si>
+  <si>
+    <t>FL_00123064</t>
+  </si>
+  <si>
+    <t>FL_00121479</t>
+  </si>
+  <si>
+    <t>FL_00470873</t>
+  </si>
+  <si>
+    <t>FL_00201163</t>
+  </si>
+  <si>
+    <t>FL_00067352</t>
+  </si>
+  <si>
+    <t>FL_00215619</t>
+  </si>
+  <si>
+    <t>FL_17478927</t>
+  </si>
+  <si>
+    <t>FL_1552390</t>
+  </si>
+  <si>
+    <t>FL_1552296</t>
+  </si>
+  <si>
+    <t>FL_17264096</t>
+  </si>
+  <si>
+    <t>FL_17016220</t>
+  </si>
+  <si>
+    <t>FL_698054</t>
+  </si>
+  <si>
+    <t>FL_17309616</t>
+  </si>
+  <si>
+    <t>FL_509572</t>
+  </si>
+  <si>
+    <t>FL_17220315</t>
+  </si>
+  <si>
+    <t>FL_571716</t>
+  </si>
+  <si>
+    <t>FL_1505827</t>
+  </si>
+  <si>
+    <t>FL_1562759</t>
+  </si>
+  <si>
+    <t>FL_17394394</t>
+  </si>
+  <si>
+    <t>FL_1556835</t>
+  </si>
+  <si>
+    <t>FL_17182286</t>
+  </si>
+  <si>
+    <t>FL_675255</t>
+  </si>
+  <si>
+    <t>FL_17344300</t>
+  </si>
+  <si>
+    <t>FL_17600273</t>
+  </si>
+  <si>
+    <t>FL_17227531</t>
+  </si>
+  <si>
+    <t>FL_17473124</t>
+  </si>
+  <si>
+    <t>FL_1546449</t>
+  </si>
+  <si>
+    <t>FL_17140078</t>
+  </si>
+  <si>
+    <t>FL_17149487</t>
+  </si>
+  <si>
+    <t>FL_17130331</t>
+  </si>
+  <si>
+    <t>FL_502969</t>
+  </si>
+  <si>
+    <t>FL_706772</t>
+  </si>
+  <si>
+    <t>FL_17010519</t>
+  </si>
+  <si>
+    <t>FL_833553</t>
+  </si>
+  <si>
+    <t>FL_17131432</t>
+  </si>
+  <si>
+    <t>FL_1549207</t>
+  </si>
+  <si>
+    <t>FL_17210562</t>
+  </si>
+  <si>
+    <t>FL_17680561</t>
+  </si>
+  <si>
+    <t>FL_17011566</t>
+  </si>
+  <si>
+    <t>FL_17691709</t>
+  </si>
+  <si>
+    <t>FL_17553512</t>
+  </si>
+  <si>
+    <t>FL_1297364</t>
+  </si>
+  <si>
+    <t>FL_17290881</t>
+  </si>
+  <si>
+    <t>FL_17378423</t>
+  </si>
+  <si>
+    <t>FL_1336297</t>
+  </si>
+  <si>
+    <t>FL_631054</t>
+  </si>
+  <si>
+    <t>FL_649514</t>
+  </si>
+  <si>
+    <t>FL_612813</t>
+  </si>
+  <si>
+    <t>FL_522018</t>
+  </si>
+  <si>
+    <t>FL_17150463</t>
+  </si>
+  <si>
+    <t>FL_17337093</t>
+  </si>
+  <si>
+    <t>FL_17357982</t>
+  </si>
+  <si>
+    <t>FL_17315980</t>
+  </si>
+  <si>
+    <t>FL_1434625</t>
+  </si>
+  <si>
+    <t>FL_17710936</t>
+  </si>
+  <si>
+    <t>FL_504261</t>
+  </si>
+  <si>
+    <t>FL_1311736</t>
+  </si>
+  <si>
+    <t>FL_503091</t>
+  </si>
+  <si>
+    <t>FL_834951</t>
+  </si>
+  <si>
+    <t>FL_17152737</t>
+  </si>
+  <si>
+    <t>FL_17665546</t>
+  </si>
+  <si>
+    <t>FL_00233632</t>
+  </si>
+  <si>
+    <t>FL_00099224</t>
+  </si>
+  <si>
+    <t>FL_00509173</t>
+  </si>
+  <si>
+    <t>FL_00271966</t>
+  </si>
+  <si>
+    <t>FL_00130213</t>
+  </si>
+  <si>
+    <t>FL_00066723</t>
+  </si>
+  <si>
+    <t>FL_00473918</t>
+  </si>
+  <si>
+    <t>FL_00129552</t>
+  </si>
+  <si>
+    <t>FL_00015371</t>
+  </si>
+  <si>
+    <t>FL_00411638</t>
+  </si>
+  <si>
+    <t>FL_00091035</t>
+  </si>
+  <si>
+    <t>FL_00161414</t>
+  </si>
+  <si>
+    <t>FL_SH005212</t>
+  </si>
+  <si>
+    <t>FL_00048384</t>
+  </si>
+  <si>
+    <t>FL_00043571</t>
+  </si>
+  <si>
+    <t>FL_00421434</t>
+  </si>
+  <si>
+    <t>FL_00090679</t>
+  </si>
+  <si>
+    <t>FL_00198865</t>
+  </si>
+  <si>
+    <t>FL_12333774</t>
+  </si>
+  <si>
+    <t>FL_00401455</t>
+  </si>
+  <si>
+    <t>FL_00205275</t>
+  </si>
+  <si>
+    <t>FL_00134304</t>
+  </si>
+  <si>
+    <t>FL_00315875</t>
+  </si>
+  <si>
+    <t>FL_00255578</t>
+  </si>
+  <si>
+    <t>FL_12306222</t>
+  </si>
+  <si>
+    <t>FL_895038</t>
+  </si>
+  <si>
+    <t>FL_847911</t>
+  </si>
+  <si>
+    <t>FL_17162787</t>
+  </si>
+  <si>
+    <t>FL_1449252</t>
+  </si>
+  <si>
+    <t>FL_17654082</t>
+  </si>
+  <si>
+    <t>FL_616698</t>
+  </si>
+  <si>
+    <t>FL_17541875</t>
+  </si>
+  <si>
+    <t>FL_17211469</t>
+  </si>
+  <si>
+    <t>FL_17157054</t>
+  </si>
+  <si>
+    <t>FL_604476</t>
+  </si>
+  <si>
+    <t>FL_768811</t>
+  </si>
+  <si>
+    <t>FL_17125934</t>
+  </si>
+  <si>
+    <t>FL_17743841</t>
+  </si>
+  <si>
+    <t>FL_504168</t>
+  </si>
+  <si>
+    <t>FL_17112865</t>
+  </si>
+  <si>
+    <t>FL_17342446</t>
+  </si>
+  <si>
+    <t>FL_17390193</t>
+  </si>
+  <si>
+    <t>FL_501364</t>
+  </si>
+  <si>
+    <t>FL_17181068</t>
+  </si>
+  <si>
+    <t>FL_835388</t>
+  </si>
+  <si>
+    <t>FL_17350490</t>
+  </si>
+  <si>
+    <t>FL_835374</t>
+  </si>
+  <si>
+    <t>FL_17673808</t>
+  </si>
+  <si>
+    <t>FL_17191088</t>
+  </si>
+  <si>
+    <t>FL_17121991</t>
+  </si>
+  <si>
+    <t>FL_17335361</t>
+  </si>
+  <si>
+    <t>FL_17176188</t>
+  </si>
+  <si>
+    <t>FL_17011130</t>
+  </si>
+  <si>
+    <t>FL_17141535</t>
+  </si>
+  <si>
+    <t>FL_17166527</t>
+  </si>
+  <si>
+    <t>FL_1496494</t>
+  </si>
+  <si>
+    <t>FL_580131</t>
+  </si>
+  <si>
+    <t>FL_596016</t>
+  </si>
+  <si>
+    <t>FL_502625</t>
+  </si>
+  <si>
+    <t>FL_1513939</t>
+  </si>
+  <si>
+    <t>FL_17037867</t>
+  </si>
+  <si>
+    <t>FL_17362138</t>
+  </si>
+  <si>
+    <t>FL_17801622</t>
+  </si>
+  <si>
+    <t>FL_17139326</t>
+  </si>
+  <si>
+    <t>FL_17346593</t>
+  </si>
+  <si>
+    <t>FL_17434785</t>
+  </si>
+  <si>
+    <t>FL_17605441</t>
+  </si>
+  <si>
+    <t>FL_17016198</t>
+  </si>
+  <si>
+    <t>FL_17190525</t>
+  </si>
+  <si>
+    <t>FL_17351943</t>
+  </si>
+  <si>
+    <t>FL_17717112</t>
+  </si>
+  <si>
+    <t>FL_966078</t>
+  </si>
+  <si>
+    <t>FL_17151519</t>
+  </si>
+  <si>
+    <t>FL_17135276</t>
+  </si>
+  <si>
+    <t>FL_974435</t>
+  </si>
+  <si>
+    <t>FL_17141227</t>
+  </si>
+  <si>
+    <t>FL_17210272</t>
+  </si>
+  <si>
+    <t>FL_833001</t>
+  </si>
+  <si>
+    <t>FL_17024360</t>
+  </si>
+  <si>
+    <t>FL_1571613</t>
+  </si>
+  <si>
+    <t>FL_17661509</t>
+  </si>
+  <si>
+    <t>FL_1310746</t>
+  </si>
+  <si>
+    <t>FL_17293400</t>
+  </si>
+  <si>
+    <t>FL_1310648</t>
+  </si>
+  <si>
+    <t>FL_830651</t>
+  </si>
+  <si>
+    <t>FL_00420652</t>
+  </si>
+  <si>
+    <t>FL_00487910</t>
+  </si>
+  <si>
+    <t>FL_00090402</t>
+  </si>
+  <si>
+    <t>FL_12330524</t>
+  </si>
+  <si>
+    <t>FL_00150330</t>
+  </si>
+  <si>
+    <t>FL_00142035</t>
+  </si>
+  <si>
+    <t>FL_00513937</t>
+  </si>
+  <si>
+    <t>FL_00016493</t>
+  </si>
+  <si>
+    <t>FL_00168660</t>
+  </si>
+  <si>
+    <t>FL_00212625</t>
+  </si>
+  <si>
+    <t>FL_00142258</t>
+  </si>
+  <si>
+    <t>FL_00142214</t>
+  </si>
+  <si>
+    <t>FL_00142032</t>
+  </si>
+  <si>
+    <t>FL_00243919</t>
+  </si>
+  <si>
+    <t>FL_00013374</t>
+  </si>
+  <si>
+    <t>FL_00437980</t>
+  </si>
+  <si>
+    <t>FL_00484325</t>
+  </si>
+  <si>
+    <t>FL_00215470</t>
+  </si>
+  <si>
+    <t>FL_00486007</t>
+  </si>
+  <si>
+    <t>FL_00225083</t>
+  </si>
+  <si>
+    <t>FL_00301580</t>
+  </si>
+  <si>
+    <t>FL_00418937</t>
+  </si>
+  <si>
+    <t>FL_00127641</t>
+  </si>
+  <si>
+    <t>FL_00066681</t>
+  </si>
+  <si>
+    <t>FL_00130517</t>
+  </si>
+  <si>
+    <t>FL_00136310</t>
+  </si>
+  <si>
+    <t>FL_12331778</t>
+  </si>
+  <si>
+    <t>FL_00130732</t>
+  </si>
+  <si>
+    <t>FL_00526480</t>
+  </si>
+  <si>
+    <t>FL_00066714</t>
+  </si>
+  <si>
+    <t>FL_00504286</t>
+  </si>
+  <si>
+    <t>FL_00212358</t>
+  </si>
+  <si>
+    <t>FL_00231137</t>
+  </si>
+  <si>
+    <t>FL_00121781</t>
+  </si>
+  <si>
+    <t>FL_00312571</t>
+  </si>
+  <si>
+    <t>FL_00065318</t>
+  </si>
+  <si>
+    <t>FL_00206221</t>
+  </si>
+  <si>
+    <t>FL_00505356</t>
+  </si>
+  <si>
+    <t>FL_00495022</t>
+  </si>
+  <si>
+    <t>FL_00293713</t>
+  </si>
+  <si>
+    <t>FL_00198792</t>
+  </si>
+  <si>
+    <t>FL_00200810</t>
+  </si>
+  <si>
+    <t>FL_00088096</t>
+  </si>
+  <si>
+    <t>FL_00198996</t>
+  </si>
+  <si>
+    <t>FL_00285381</t>
+  </si>
+  <si>
+    <t>FL_00237814</t>
+  </si>
+  <si>
+    <t>FL_00473684</t>
+  </si>
+  <si>
+    <t>FL_00237917</t>
+  </si>
+  <si>
+    <t>FL_00131546</t>
+  </si>
+  <si>
+    <t>FL_00238359</t>
+  </si>
+  <si>
+    <t>FL_00236841</t>
+  </si>
+  <si>
+    <t>FL_00233535</t>
+  </si>
+  <si>
+    <t>FL_00099992</t>
+  </si>
+  <si>
+    <t>FL_00071688</t>
+  </si>
+  <si>
+    <t>FL_00543973</t>
+  </si>
+  <si>
+    <t>FL_00441571</t>
+  </si>
+  <si>
+    <t>FL_00235431</t>
+  </si>
+  <si>
+    <t>FL_00281611</t>
+  </si>
+  <si>
+    <t>FL_00247845</t>
+  </si>
+  <si>
+    <t>FL_00495129</t>
+  </si>
+  <si>
+    <t>FL_00549122</t>
+  </si>
+  <si>
+    <t>FL_829685</t>
+  </si>
+  <si>
+    <t>FL_17177456</t>
+  </si>
+  <si>
+    <t>FL_17215537</t>
+  </si>
+  <si>
+    <t>FL_17188880</t>
+  </si>
+  <si>
+    <t>FL_1461999</t>
+  </si>
+  <si>
+    <t>FL_603440</t>
+  </si>
+  <si>
+    <t>FL_17214724</t>
+  </si>
+  <si>
+    <t>FL_517861</t>
+  </si>
+  <si>
+    <t>FL_17108856</t>
+  </si>
+  <si>
+    <t>FL_829648</t>
+  </si>
+  <si>
+    <t>FL_1451305</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Indosat Regular"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -3069,8 +4385,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3101,8 +4423,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCFF5F1"/>
+        <bgColor rgb="FFCFF5F1"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -3132,13 +4460,41 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF70E2D7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF70E2D7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3152,31 +4508,48 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="3" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="4" applyFont="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="5">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="2" xr:uid="{E236E5E2-E961-44E9-8599-DB5AE1BB3BE1}"/>
     <cellStyle name="Normal 2 2" xfId="1" xr:uid="{0F1D241C-5F10-4255-8175-7C68425309E2}"/>
+    <cellStyle name="Normal 3" xfId="3" xr:uid="{A74063DA-D7D8-4914-996D-7028403EEC31}"/>
+    <cellStyle name="Normal 4" xfId="4" xr:uid="{C06BD901-4FA7-4F8F-B665-C54CF1A377E8}"/>
   </cellStyles>
   <dxfs count="174">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -3194,16 +4567,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3229,21 +4592,21 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
         <patternFill>
           <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3309,11 +4672,31 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C5700"/>
       </font>
       <fill>
         <patternFill>
           <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3329,41 +4712,11 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF9C5700"/>
       </font>
       <fill>
         <patternFill>
           <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3414,6 +4767,16 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3509,6 +4872,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C5700"/>
       </font>
       <fill>
@@ -3524,16 +4897,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3589,11 +4952,11 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C5700"/>
+        <color rgb="FF006100"/>
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3619,6 +4982,26 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -3629,11 +5012,71 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3659,36 +5102,6 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF9C5700"/>
       </font>
       <fill>
@@ -3704,56 +5117,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3839,21 +5202,21 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
         <patternFill>
           <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3969,21 +5332,21 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C5700"/>
       </font>
       <fill>
         <patternFill>
           <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -4029,21 +5392,21 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C5700"/>
       </font>
       <fill>
         <patternFill>
           <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -4119,6 +5482,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -4159,16 +5532,6 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -4194,6 +5557,36 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -4299,36 +5692,6 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -4344,236 +5707,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -4639,6 +5772,36 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -4649,11 +5812,41 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
+        <color rgb="FF9C5700"/>
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -4674,6 +5867,76 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -4789,11 +6052,21 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF006100"/>
+        <color rgb="FF9C0006"/>
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -4839,6 +6112,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -4849,11 +6132,91 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C5700"/>
       </font>
       <fill>
         <patternFill>
           <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -5247,7 +6610,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A746E14-DA6E-4106-846A-771E18ABB4AC}">
-  <dimension ref="A1:D998"/>
+  <dimension ref="A1:D1454"/>
   <sheetFormatPr defaultColWidth="8.640625" defaultRowHeight="17.5" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="1" max="1" width="8.42578125" bestFit="1" customWidth="1"/>
@@ -19058,59 +20421,59 @@
       </c>
     </row>
     <row r="987" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A987" s="10" t="s">
-        <v>988</v>
-      </c>
-      <c r="B987" s="11" t="s">
+      <c r="A987" s="12" t="s">
+        <v>570</v>
+      </c>
+      <c r="B987">
+        <v>2613051248</v>
+      </c>
+      <c r="C987" s="10" t="s">
+        <v>571</v>
+      </c>
+      <c r="D987" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="988" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A988" s="12" t="s">
+        <v>570</v>
+      </c>
+      <c r="B988" t="s">
         <v>989</v>
       </c>
-      <c r="C987" s="10" t="s">
-        <v>571</v>
-      </c>
-      <c r="D987" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="988" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A988" s="10" t="s">
-        <v>990</v>
-      </c>
-      <c r="B988" s="11" t="s">
-        <v>991</v>
-      </c>
       <c r="C988" s="10" t="s">
         <v>571</v>
       </c>
       <c r="D988" t="s">
-        <v>76</v>
+        <v>28</v>
       </c>
     </row>
     <row r="989" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A989" s="10" t="s">
-        <v>988</v>
-      </c>
-      <c r="B989" s="11" t="s">
-        <v>992</v>
+      <c r="A989" s="12" t="s">
+        <v>570</v>
+      </c>
+      <c r="B989">
+        <v>2613051223</v>
       </c>
       <c r="C989" s="10" t="s">
         <v>571</v>
       </c>
       <c r="D989" t="s">
-        <v>6</v>
+        <v>85</v>
       </c>
     </row>
     <row r="990" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A990" s="10" t="s">
-        <v>990</v>
-      </c>
-      <c r="B990" s="11" t="s">
-        <v>993</v>
+      <c r="A990" s="12" t="s">
+        <v>570</v>
+      </c>
+      <c r="B990">
+        <v>2613051222</v>
       </c>
       <c r="C990" s="10" t="s">
         <v>571</v>
       </c>
       <c r="D990" t="s">
-        <v>6</v>
+        <v>85</v>
       </c>
     </row>
     <row r="991" spans="1:4" x14ac:dyDescent="0.5">
@@ -19118,13 +20481,13 @@
         <v>570</v>
       </c>
       <c r="B991">
-        <v>2613051248</v>
+        <v>2613051172</v>
       </c>
       <c r="C991" s="10" t="s">
         <v>571</v>
       </c>
       <c r="D991" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
     </row>
     <row r="992" spans="1:4" x14ac:dyDescent="0.5">
@@ -19132,13 +20495,13 @@
         <v>570</v>
       </c>
       <c r="B992" t="s">
-        <v>994</v>
+        <v>990</v>
       </c>
       <c r="C992" s="10" t="s">
         <v>571</v>
       </c>
       <c r="D992" t="s">
-        <v>28</v>
+        <v>113</v>
       </c>
     </row>
     <row r="993" spans="1:4" x14ac:dyDescent="0.5">
@@ -19146,7 +20509,7 @@
         <v>570</v>
       </c>
       <c r="B993">
-        <v>2613051223</v>
+        <v>2613051349</v>
       </c>
       <c r="C993" s="10" t="s">
         <v>571</v>
@@ -19160,69 +20523,6453 @@
         <v>570</v>
       </c>
       <c r="B994">
-        <v>2613051222</v>
+        <v>2613051179</v>
       </c>
       <c r="C994" s="10" t="s">
         <v>571</v>
       </c>
       <c r="D994" t="s">
-        <v>85</v>
+        <v>114</v>
       </c>
     </row>
     <row r="995" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A995" s="12" t="s">
-        <v>570</v>
-      </c>
-      <c r="B995">
-        <v>2613051172</v>
+        <v>991</v>
+      </c>
+      <c r="B995" s="14">
+        <v>12333108</v>
       </c>
       <c r="C995" s="10" t="s">
         <v>571</v>
       </c>
       <c r="D995" t="s">
-        <v>113</v>
+        <v>77</v>
       </c>
     </row>
     <row r="996" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A996" s="12" t="s">
-        <v>570</v>
-      </c>
-      <c r="B996" t="s">
-        <v>995</v>
+        <v>991</v>
+      </c>
+      <c r="B996" s="15">
+        <v>12333658</v>
       </c>
       <c r="C996" s="10" t="s">
         <v>571</v>
       </c>
       <c r="D996" t="s">
-        <v>113</v>
+        <v>78</v>
       </c>
     </row>
     <row r="997" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A997" s="12" t="s">
-        <v>570</v>
-      </c>
-      <c r="B997">
-        <v>2613051349</v>
+        <v>991</v>
+      </c>
+      <c r="B997" s="14">
+        <v>12330795</v>
       </c>
       <c r="C997" s="10" t="s">
         <v>571</v>
       </c>
       <c r="D997" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
     </row>
     <row r="998" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A998" s="12" t="s">
-        <v>570</v>
-      </c>
-      <c r="B998">
-        <v>2613051179</v>
+        <v>991</v>
+      </c>
+      <c r="B998" s="15">
+        <v>12331176</v>
       </c>
       <c r="C998" s="10" t="s">
         <v>571</v>
       </c>
       <c r="D998" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="999" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A999" s="12" t="s">
+        <v>991</v>
+      </c>
+      <c r="B999" s="14">
+        <v>12331710</v>
+      </c>
+      <c r="C999" s="10" t="s">
+        <v>571</v>
+      </c>
+      <c r="D999" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="1000" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1000" s="12" t="s">
+        <v>991</v>
+      </c>
+      <c r="B1000" s="15">
+        <v>12331332</v>
+      </c>
+      <c r="C1000" s="10" t="s">
+        <v>571</v>
+      </c>
+      <c r="D1000" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="1001" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1001" s="12" t="s">
+        <v>991</v>
+      </c>
+      <c r="B1001" s="14">
+        <v>12360184</v>
+      </c>
+      <c r="C1001" s="10" t="s">
+        <v>571</v>
+      </c>
+      <c r="D1001" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="1002" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1002" s="12" t="s">
+        <v>991</v>
+      </c>
+      <c r="B1002" s="15">
+        <v>12360192</v>
+      </c>
+      <c r="C1002" s="10" t="s">
+        <v>571</v>
+      </c>
+      <c r="D1002" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="1003" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1003" s="12" t="s">
+        <v>991</v>
+      </c>
+      <c r="B1003" s="15">
+        <v>12331124</v>
+      </c>
+      <c r="C1003" s="10" t="s">
+        <v>571</v>
+      </c>
+      <c r="D1003" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="1004" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1004" s="12" t="s">
+        <v>991</v>
+      </c>
+      <c r="B1004" s="14">
+        <v>12331472</v>
+      </c>
+      <c r="C1004" s="10" t="s">
+        <v>571</v>
+      </c>
+      <c r="D1004" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="1005" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1005" s="12" t="s">
+        <v>991</v>
+      </c>
+      <c r="B1005" s="15">
+        <v>12331475</v>
+      </c>
+      <c r="C1005" s="10" t="s">
+        <v>571</v>
+      </c>
+      <c r="D1005" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="1006" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1006" s="12" t="s">
+        <v>991</v>
+      </c>
+      <c r="B1006" s="14">
+        <v>12331125</v>
+      </c>
+      <c r="C1006" s="10" t="s">
+        <v>571</v>
+      </c>
+      <c r="D1006" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="1007" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1007" s="12" t="s">
+        <v>991</v>
+      </c>
+      <c r="B1007" s="15">
+        <v>1206744</v>
+      </c>
+      <c r="C1007" s="10" t="s">
+        <v>571</v>
+      </c>
+      <c r="D1007" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="1008" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1008" s="12" t="s">
+        <v>991</v>
+      </c>
+      <c r="B1008" s="14">
+        <v>12330708</v>
+      </c>
+      <c r="C1008" s="10" t="s">
+        <v>571</v>
+      </c>
+      <c r="D1008" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="1009" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1009" s="12" t="s">
+        <v>991</v>
+      </c>
+      <c r="B1009" s="15">
+        <v>12330724</v>
+      </c>
+      <c r="C1009" s="10" t="s">
+        <v>571</v>
+      </c>
+      <c r="D1009" t="s">
         <v>114</v>
+      </c>
+    </row>
+    <row r="1010" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1010" s="12" t="s">
+        <v>991</v>
+      </c>
+      <c r="B1010" s="14">
+        <v>12331559</v>
+      </c>
+      <c r="C1010" s="10" t="s">
+        <v>571</v>
+      </c>
+      <c r="D1010" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="1011" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1011" s="12" t="s">
+        <v>991</v>
+      </c>
+      <c r="B1011" s="15">
+        <v>12330913</v>
+      </c>
+      <c r="C1011" s="10" t="s">
+        <v>571</v>
+      </c>
+      <c r="D1011" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="1012" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1012" s="12" t="s">
+        <v>991</v>
+      </c>
+      <c r="B1012" s="14">
+        <v>12333805</v>
+      </c>
+      <c r="C1012" s="10" t="s">
+        <v>571</v>
+      </c>
+      <c r="D1012" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="1013" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1013" s="12" t="s">
+        <v>991</v>
+      </c>
+      <c r="B1013" s="15">
+        <v>12331952</v>
+      </c>
+      <c r="C1013" s="10" t="s">
+        <v>571</v>
+      </c>
+      <c r="D1013" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="1014" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1014" s="12" t="s">
+        <v>991</v>
+      </c>
+      <c r="B1014" s="14">
+        <v>12330800</v>
+      </c>
+      <c r="C1014" s="10" t="s">
+        <v>571</v>
+      </c>
+      <c r="D1014" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="1015" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1015" s="12" t="s">
+        <v>991</v>
+      </c>
+      <c r="B1015" s="15">
+        <v>12331533</v>
+      </c>
+      <c r="C1015" s="10" t="s">
+        <v>571</v>
+      </c>
+      <c r="D1015" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="1016" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1016" s="12" t="s">
+        <v>991</v>
+      </c>
+      <c r="B1016" s="14">
+        <v>12331960</v>
+      </c>
+      <c r="C1016" s="10" t="s">
+        <v>571</v>
+      </c>
+      <c r="D1016" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="1017" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1017" s="12" t="s">
+        <v>991</v>
+      </c>
+      <c r="B1017" s="13" t="s">
+        <v>992</v>
+      </c>
+      <c r="C1017" s="10" t="s">
+        <v>571</v>
+      </c>
+      <c r="D1017" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1018" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1018" s="12" t="s">
+        <v>991</v>
+      </c>
+      <c r="B1018" s="16" t="s">
+        <v>993</v>
+      </c>
+      <c r="C1018" s="10" t="s">
+        <v>571</v>
+      </c>
+      <c r="D1018" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="1019" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1019" s="12" t="s">
+        <v>991</v>
+      </c>
+      <c r="B1019" s="13" t="s">
+        <v>994</v>
+      </c>
+      <c r="C1019" s="10" t="s">
+        <v>571</v>
+      </c>
+      <c r="D1019" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="1020" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1020" s="12" t="s">
+        <v>991</v>
+      </c>
+      <c r="B1020" s="16" t="s">
+        <v>995</v>
+      </c>
+      <c r="C1020" s="10" t="s">
+        <v>571</v>
+      </c>
+      <c r="D1020" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1021" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1021" s="12" t="s">
+        <v>991</v>
+      </c>
+      <c r="B1021" s="13" t="s">
+        <v>996</v>
+      </c>
+      <c r="C1021" s="10" t="s">
+        <v>571</v>
+      </c>
+      <c r="D1021" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1022" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1022" s="12" t="s">
+        <v>991</v>
+      </c>
+      <c r="B1022" s="16" t="s">
+        <v>997</v>
+      </c>
+      <c r="C1022" s="10" t="s">
+        <v>571</v>
+      </c>
+      <c r="D1022" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="1023" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1023" s="12" t="s">
+        <v>991</v>
+      </c>
+      <c r="B1023" s="13" t="s">
+        <v>998</v>
+      </c>
+      <c r="C1023" s="10" t="s">
+        <v>571</v>
+      </c>
+      <c r="D1023" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="1024" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1024" s="12" t="s">
+        <v>991</v>
+      </c>
+      <c r="B1024" s="16" t="s">
+        <v>999</v>
+      </c>
+      <c r="C1024" s="10" t="s">
+        <v>571</v>
+      </c>
+      <c r="D1024" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1025" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1025" s="12" t="s">
+        <v>991</v>
+      </c>
+      <c r="B1025" s="13" t="s">
+        <v>1000</v>
+      </c>
+      <c r="C1025" s="10" t="s">
+        <v>571</v>
+      </c>
+      <c r="D1025" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="1026" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1026" s="12" t="s">
+        <v>991</v>
+      </c>
+      <c r="B1026" s="16" t="s">
+        <v>1001</v>
+      </c>
+      <c r="C1026" s="10" t="s">
+        <v>571</v>
+      </c>
+      <c r="D1026" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1027" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1027" s="12" t="s">
+        <v>991</v>
+      </c>
+      <c r="B1027" s="13" t="s">
+        <v>1002</v>
+      </c>
+      <c r="C1027" s="10" t="s">
+        <v>571</v>
+      </c>
+      <c r="D1027" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="1028" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1028" s="12" t="s">
+        <v>991</v>
+      </c>
+      <c r="B1028" s="16" t="s">
+        <v>1003</v>
+      </c>
+      <c r="C1028" s="10" t="s">
+        <v>571</v>
+      </c>
+      <c r="D1028" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="1029" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1029" s="12" t="s">
+        <v>991</v>
+      </c>
+      <c r="B1029" s="13" t="s">
+        <v>1004</v>
+      </c>
+      <c r="C1029" s="10" t="s">
+        <v>571</v>
+      </c>
+      <c r="D1029" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="1030" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1030" s="12" t="s">
+        <v>991</v>
+      </c>
+      <c r="B1030" s="16" t="s">
+        <v>1005</v>
+      </c>
+      <c r="C1030" s="10" t="s">
+        <v>571</v>
+      </c>
+      <c r="D1030" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="1031" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1031" s="12" t="s">
+        <v>991</v>
+      </c>
+      <c r="B1031" s="13" t="s">
+        <v>1006</v>
+      </c>
+      <c r="C1031" s="10" t="s">
+        <v>571</v>
+      </c>
+      <c r="D1031" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1032" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1032" s="12" t="s">
+        <v>991</v>
+      </c>
+      <c r="B1032" s="16" t="s">
+        <v>1007</v>
+      </c>
+      <c r="C1032" s="10" t="s">
+        <v>571</v>
+      </c>
+      <c r="D1032" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1033" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1033" s="12" t="s">
+        <v>991</v>
+      </c>
+      <c r="B1033" s="13" t="s">
+        <v>1008</v>
+      </c>
+      <c r="C1033" s="10" t="s">
+        <v>571</v>
+      </c>
+      <c r="D1033" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1034" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1034" s="12" t="s">
+        <v>991</v>
+      </c>
+      <c r="B1034" s="16" t="s">
+        <v>1009</v>
+      </c>
+      <c r="C1034" s="10" t="s">
+        <v>571</v>
+      </c>
+      <c r="D1034" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="1035" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1035" s="12" t="s">
+        <v>991</v>
+      </c>
+      <c r="B1035" s="13" t="s">
+        <v>1010</v>
+      </c>
+      <c r="C1035" s="10" t="s">
+        <v>571</v>
+      </c>
+      <c r="D1035" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="1036" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1036" s="12" t="s">
+        <v>991</v>
+      </c>
+      <c r="B1036" s="16" t="s">
+        <v>1011</v>
+      </c>
+      <c r="C1036" s="10" t="s">
+        <v>571</v>
+      </c>
+      <c r="D1036" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="1037" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1037" s="12" t="s">
+        <v>991</v>
+      </c>
+      <c r="B1037" s="13" t="s">
+        <v>1012</v>
+      </c>
+      <c r="C1037" s="10" t="s">
+        <v>571</v>
+      </c>
+      <c r="D1037" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="1038" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1038" s="12" t="s">
+        <v>991</v>
+      </c>
+      <c r="B1038" s="16" t="s">
+        <v>1013</v>
+      </c>
+      <c r="C1038" s="10" t="s">
+        <v>571</v>
+      </c>
+      <c r="D1038" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="1039" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1039" s="12" t="s">
+        <v>991</v>
+      </c>
+      <c r="B1039" s="13" t="s">
+        <v>1014</v>
+      </c>
+      <c r="C1039" s="10" t="s">
+        <v>571</v>
+      </c>
+      <c r="D1039" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="1040" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1040" s="12" t="s">
+        <v>991</v>
+      </c>
+      <c r="B1040" s="16" t="s">
+        <v>1015</v>
+      </c>
+      <c r="C1040" s="10" t="s">
+        <v>571</v>
+      </c>
+      <c r="D1040" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="1041" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1041" s="12" t="s">
+        <v>991</v>
+      </c>
+      <c r="B1041" s="13" t="s">
+        <v>1016</v>
+      </c>
+      <c r="C1041" s="10" t="s">
+        <v>571</v>
+      </c>
+      <c r="D1041" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1042" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1042" s="12" t="s">
+        <v>991</v>
+      </c>
+      <c r="B1042" s="16" t="s">
+        <v>1017</v>
+      </c>
+      <c r="C1042" s="10" t="s">
+        <v>571</v>
+      </c>
+      <c r="D1042" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="1043" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1043" s="12" t="s">
+        <v>991</v>
+      </c>
+      <c r="B1043" s="13" t="s">
+        <v>1018</v>
+      </c>
+      <c r="C1043" s="10" t="s">
+        <v>571</v>
+      </c>
+      <c r="D1043" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="1044" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1044" s="12" t="s">
+        <v>991</v>
+      </c>
+      <c r="B1044" s="13" t="s">
+        <v>1018</v>
+      </c>
+      <c r="C1044" s="10" t="s">
+        <v>571</v>
+      </c>
+      <c r="D1044" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="1045" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1045" s="12" t="s">
+        <v>991</v>
+      </c>
+      <c r="B1045" s="13" t="s">
+        <v>1019</v>
+      </c>
+      <c r="C1045" s="10" t="s">
+        <v>571</v>
+      </c>
+      <c r="D1045" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="1046" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1046" s="12" t="s">
+        <v>991</v>
+      </c>
+      <c r="B1046" s="16" t="s">
+        <v>1020</v>
+      </c>
+      <c r="C1046" s="10" t="s">
+        <v>571</v>
+      </c>
+      <c r="D1046" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="1047" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1047" s="12" t="s">
+        <v>991</v>
+      </c>
+      <c r="B1047" s="13" t="s">
+        <v>1021</v>
+      </c>
+      <c r="C1047" s="10" t="s">
+        <v>571</v>
+      </c>
+      <c r="D1047" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="1048" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1048" s="12" t="s">
+        <v>991</v>
+      </c>
+      <c r="B1048" s="16" t="s">
+        <v>1022</v>
+      </c>
+      <c r="C1048" s="10" t="s">
+        <v>571</v>
+      </c>
+      <c r="D1048" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="1049" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1049" s="12" t="s">
+        <v>991</v>
+      </c>
+      <c r="B1049" s="13" t="s">
+        <v>1023</v>
+      </c>
+      <c r="C1049" s="10" t="s">
+        <v>571</v>
+      </c>
+      <c r="D1049" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="1050" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1050" s="12" t="s">
+        <v>991</v>
+      </c>
+      <c r="B1050" s="16" t="s">
+        <v>1024</v>
+      </c>
+      <c r="C1050" s="10" t="s">
+        <v>571</v>
+      </c>
+      <c r="D1050" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="1051" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1051" s="12" t="s">
+        <v>991</v>
+      </c>
+      <c r="B1051" s="13" t="s">
+        <v>1025</v>
+      </c>
+      <c r="C1051" s="10" t="s">
+        <v>571</v>
+      </c>
+      <c r="D1051" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="1052" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1052" s="12" t="s">
+        <v>991</v>
+      </c>
+      <c r="B1052" s="16" t="s">
+        <v>1026</v>
+      </c>
+      <c r="C1052" s="10" t="s">
+        <v>571</v>
+      </c>
+      <c r="D1052" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="1053" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1053" s="12" t="s">
+        <v>991</v>
+      </c>
+      <c r="B1053" s="16" t="s">
+        <v>1027</v>
+      </c>
+      <c r="C1053" s="10" t="s">
+        <v>571</v>
+      </c>
+      <c r="D1053" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1054" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1054" s="12" t="s">
+        <v>991</v>
+      </c>
+      <c r="B1054" s="13" t="s">
+        <v>1028</v>
+      </c>
+      <c r="C1054" s="10" t="s">
+        <v>571</v>
+      </c>
+      <c r="D1054" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1055" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1055" s="12" t="s">
+        <v>991</v>
+      </c>
+      <c r="B1055" s="16" t="s">
+        <v>1029</v>
+      </c>
+      <c r="C1055" s="10" t="s">
+        <v>571</v>
+      </c>
+      <c r="D1055" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1056" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1056" s="12" t="s">
+        <v>991</v>
+      </c>
+      <c r="B1056" s="13" t="s">
+        <v>1030</v>
+      </c>
+      <c r="C1056" s="10" t="s">
+        <v>571</v>
+      </c>
+      <c r="D1056" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1057" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1057" s="12" t="s">
+        <v>991</v>
+      </c>
+      <c r="B1057" s="16" t="s">
+        <v>1031</v>
+      </c>
+      <c r="C1057" s="10" t="s">
+        <v>571</v>
+      </c>
+      <c r="D1057" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1058" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1058" s="12" t="s">
+        <v>991</v>
+      </c>
+      <c r="B1058" s="13" t="s">
+        <v>1032</v>
+      </c>
+      <c r="C1058" s="10" t="s">
+        <v>571</v>
+      </c>
+      <c r="D1058" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1059" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1059" s="12" t="s">
+        <v>991</v>
+      </c>
+      <c r="B1059" s="16" t="s">
+        <v>1033</v>
+      </c>
+      <c r="C1059" s="10" t="s">
+        <v>571</v>
+      </c>
+      <c r="D1059" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1060" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1060" s="12" t="s">
+        <v>991</v>
+      </c>
+      <c r="B1060" s="13" t="s">
+        <v>1034</v>
+      </c>
+      <c r="C1060" s="10" t="s">
+        <v>571</v>
+      </c>
+      <c r="D1060" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1061" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1061" s="12" t="s">
+        <v>991</v>
+      </c>
+      <c r="B1061" s="16" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C1061" s="10" t="s">
+        <v>571</v>
+      </c>
+      <c r="D1061" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1062" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1062" s="12" t="s">
+        <v>991</v>
+      </c>
+      <c r="B1062" s="13" t="s">
+        <v>1036</v>
+      </c>
+      <c r="C1062" s="10" t="s">
+        <v>571</v>
+      </c>
+      <c r="D1062" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1063" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1063" s="12" t="s">
+        <v>991</v>
+      </c>
+      <c r="B1063" s="16" t="s">
+        <v>1037</v>
+      </c>
+      <c r="C1063" s="10" t="s">
+        <v>571</v>
+      </c>
+      <c r="D1063" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1064" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1064" s="12" t="s">
+        <v>991</v>
+      </c>
+      <c r="B1064" s="16" t="s">
+        <v>1038</v>
+      </c>
+      <c r="C1064" s="10" t="s">
+        <v>571</v>
+      </c>
+      <c r="D1064" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1065" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1065" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1065" s="17" t="s">
+        <v>1039</v>
+      </c>
+      <c r="C1065" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1065" s="17" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="1066" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1066" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1066" s="17" t="s">
+        <v>1041</v>
+      </c>
+      <c r="C1066" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1066" s="17" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="1067" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1067" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1067" s="17" t="s">
+        <v>1042</v>
+      </c>
+      <c r="C1067" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1067" s="17" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="1068" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1068" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1068" s="17" t="s">
+        <v>1043</v>
+      </c>
+      <c r="C1068" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1068" s="17" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="1069" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1069" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1069" s="17" t="s">
+        <v>1044</v>
+      </c>
+      <c r="C1069" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1069" s="17" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="1070" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1070" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1070" s="17" t="s">
+        <v>1045</v>
+      </c>
+      <c r="C1070" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1070" s="17" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="1071" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1071" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1071" s="17" t="s">
+        <v>1046</v>
+      </c>
+      <c r="C1071" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1071" s="17" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="1072" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1072" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1072" s="17" t="s">
+        <v>1047</v>
+      </c>
+      <c r="C1072" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1072" s="17" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="1073" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1073" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1073" s="17" t="s">
+        <v>1048</v>
+      </c>
+      <c r="C1073" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1073" s="17" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="1074" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1074" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1074" s="17" t="s">
+        <v>1049</v>
+      </c>
+      <c r="C1074" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1074" s="17" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="1075" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1075" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1075" s="17" t="s">
+        <v>1050</v>
+      </c>
+      <c r="C1075" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1075" s="17" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="1076" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1076" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1076" s="17" t="s">
+        <v>1051</v>
+      </c>
+      <c r="C1076" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1076" s="17" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="1077" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1077" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1077" s="17" t="s">
+        <v>1052</v>
+      </c>
+      <c r="C1077" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1077" s="17" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1078" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1078" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1078" s="17" t="s">
+        <v>1053</v>
+      </c>
+      <c r="C1078" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1078" s="17" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1079" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1079" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1079" s="17" t="s">
+        <v>1054</v>
+      </c>
+      <c r="C1079" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1079" s="17" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1080" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1080" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1080" s="17" t="s">
+        <v>1055</v>
+      </c>
+      <c r="C1080" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1080" s="17" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1081" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1081" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1081" s="17" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C1081" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1081" s="17" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1082" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1082" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1082" s="17" t="s">
+        <v>1057</v>
+      </c>
+      <c r="C1082" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1082" s="17" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1083" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1083" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1083" s="17" t="s">
+        <v>1058</v>
+      </c>
+      <c r="C1083" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1083" s="17" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1084" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1084" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1084" s="17" t="s">
+        <v>1059</v>
+      </c>
+      <c r="C1084" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1084" s="17" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="1085" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1085" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1085" s="17" t="s">
+        <v>1060</v>
+      </c>
+      <c r="C1085" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1085" s="17" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="1086" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1086" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1086" s="17" t="s">
+        <v>1061</v>
+      </c>
+      <c r="C1086" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1086" s="17" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="1087" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1087" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1087" s="17" t="s">
+        <v>1062</v>
+      </c>
+      <c r="C1087" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1087" s="17" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="1088" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1088" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1088" s="17" t="s">
+        <v>1063</v>
+      </c>
+      <c r="C1088" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1088" s="17" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="1089" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1089" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1089" s="17" t="s">
+        <v>1064</v>
+      </c>
+      <c r="C1089" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1089" s="17" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="1090" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1090" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1090" s="17" t="s">
+        <v>1065</v>
+      </c>
+      <c r="C1090" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1090" s="17" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="1091" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1091" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1091" s="17" t="s">
+        <v>1066</v>
+      </c>
+      <c r="C1091" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1091" s="17" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="1092" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1092" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1092" s="17" t="s">
+        <v>1067</v>
+      </c>
+      <c r="C1092" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1092" s="17" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="1093" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1093" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1093" s="17" t="s">
+        <v>1068</v>
+      </c>
+      <c r="C1093" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1093" s="17" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="1094" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1094" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1094" s="17" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C1094" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1094" s="17" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="1095" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1095" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1095" s="17" t="s">
+        <v>1070</v>
+      </c>
+      <c r="C1095" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1095" s="17" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="1096" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1096" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1096" s="17" t="s">
+        <v>1071</v>
+      </c>
+      <c r="C1096" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1096" s="17" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="1097" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1097" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1097" s="17" t="s">
+        <v>1072</v>
+      </c>
+      <c r="C1097" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1097" s="17" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="1098" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1098" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1098" s="17" t="s">
+        <v>1073</v>
+      </c>
+      <c r="C1098" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1098" s="17" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="1099" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1099" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1099" s="17" t="s">
+        <v>1074</v>
+      </c>
+      <c r="C1099" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1099" s="17" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="1100" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1100" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1100" s="17" t="s">
+        <v>1075</v>
+      </c>
+      <c r="C1100" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1100" s="17" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="1101" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1101" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1101" s="17" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C1101" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1101" s="17" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="1102" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1102" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1102" s="17" t="s">
+        <v>1077</v>
+      </c>
+      <c r="C1102" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1102" s="17" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="1103" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1103" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1103" s="17" t="s">
+        <v>1078</v>
+      </c>
+      <c r="C1103" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1103" s="17" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="1104" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1104" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1104" s="17" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C1104" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1104" s="17" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="1105" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1105" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1105" s="17" t="s">
+        <v>1080</v>
+      </c>
+      <c r="C1105" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1105" s="17" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="1106" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1106" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1106" s="17" t="s">
+        <v>1081</v>
+      </c>
+      <c r="C1106" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1106" s="17" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="1107" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1107" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1107" s="17" t="s">
+        <v>1082</v>
+      </c>
+      <c r="C1107" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1107" s="17" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="1108" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1108" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1108" s="17" t="s">
+        <v>1083</v>
+      </c>
+      <c r="C1108" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1108" s="17" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="1109" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1109" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1109" s="17" t="s">
+        <v>1084</v>
+      </c>
+      <c r="C1109" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1109" s="17" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="1110" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1110" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1110" s="17" t="s">
+        <v>1085</v>
+      </c>
+      <c r="C1110" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1110" s="17" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="1111" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1111" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1111" s="17" t="s">
+        <v>1086</v>
+      </c>
+      <c r="C1111" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1111" s="17" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="1112" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1112" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1112" s="17" t="s">
+        <v>1087</v>
+      </c>
+      <c r="C1112" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1112" s="17" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="1113" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1113" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1113" s="17" t="s">
+        <v>1088</v>
+      </c>
+      <c r="C1113" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1113" s="17" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="1114" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1114" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1114" s="17" t="s">
+        <v>1089</v>
+      </c>
+      <c r="C1114" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1114" s="17" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="1115" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1115" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1115" s="17" t="s">
+        <v>1090</v>
+      </c>
+      <c r="C1115" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1115" s="17" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="1116" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1116" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1116" s="17" t="s">
+        <v>1091</v>
+      </c>
+      <c r="C1116" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1116" s="17" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="1117" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1117" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1117" s="17" t="s">
+        <v>1092</v>
+      </c>
+      <c r="C1117" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1117" s="17" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="1118" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1118" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1118" s="17" t="s">
+        <v>1093</v>
+      </c>
+      <c r="C1118" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1118" s="17" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="1119" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1119" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1119" s="17" t="s">
+        <v>1094</v>
+      </c>
+      <c r="C1119" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1119" s="17" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="1120" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1120" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1120" s="17" t="s">
+        <v>1095</v>
+      </c>
+      <c r="C1120" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1120" s="17" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="1121" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1121" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1121" s="17" t="s">
+        <v>1096</v>
+      </c>
+      <c r="C1121" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1121" s="17" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="1122" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1122" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1122" s="17" t="s">
+        <v>1097</v>
+      </c>
+      <c r="C1122" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1122" s="17" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="1123" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1123" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1123" s="17" t="s">
+        <v>1098</v>
+      </c>
+      <c r="C1123" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1123" s="17" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="1124" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1124" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1124" s="17" t="s">
+        <v>1099</v>
+      </c>
+      <c r="C1124" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1124" s="17" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="1125" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1125" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1125" s="17" t="s">
+        <v>1100</v>
+      </c>
+      <c r="C1125" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1125" s="17" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="1126" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1126" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1126" s="17" t="s">
+        <v>1101</v>
+      </c>
+      <c r="C1126" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1126" s="17" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="1127" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1127" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1127" s="17" t="s">
+        <v>1102</v>
+      </c>
+      <c r="C1127" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1127" s="17" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="1128" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1128" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1128" s="17" t="s">
+        <v>1103</v>
+      </c>
+      <c r="C1128" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1128" s="17" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="1129" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1129" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1129" s="17" t="s">
+        <v>1104</v>
+      </c>
+      <c r="C1129" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1129" s="17" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="1130" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1130" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1130" s="17" t="s">
+        <v>1105</v>
+      </c>
+      <c r="C1130" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1130" s="17" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="1131" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1131" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1131" s="17" t="s">
+        <v>1106</v>
+      </c>
+      <c r="C1131" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1131" s="17" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="1132" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1132" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1132" s="17" t="s">
+        <v>1107</v>
+      </c>
+      <c r="C1132" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1132" s="17" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1133" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1133" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1133" s="17" t="s">
+        <v>1108</v>
+      </c>
+      <c r="C1133" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1133" s="17" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1134" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1134" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1134" s="17" t="s">
+        <v>1109</v>
+      </c>
+      <c r="C1134" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1134" s="17" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1135" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1135" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1135" s="17" t="s">
+        <v>1110</v>
+      </c>
+      <c r="C1135" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1135" s="17" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1136" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1136" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1136" s="17" t="s">
+        <v>1111</v>
+      </c>
+      <c r="C1136" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1136" s="17" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1137" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1137" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1137" s="17" t="s">
+        <v>1112</v>
+      </c>
+      <c r="C1137" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1137" s="17" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1138" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1138" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1138" s="17" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C1138" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1138" s="17" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1139" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1139" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1139" s="17" t="s">
+        <v>1114</v>
+      </c>
+      <c r="C1139" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1139" s="17" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1140" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1140" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1140" s="17" t="s">
+        <v>1115</v>
+      </c>
+      <c r="C1140" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1140" s="17" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1141" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1141" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1141" s="17" t="s">
+        <v>1116</v>
+      </c>
+      <c r="C1141" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1141" s="17" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="1142" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1142" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1142" s="17" t="s">
+        <v>1117</v>
+      </c>
+      <c r="C1142" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1142" s="17" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="1143" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1143" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1143" s="17" t="s">
+        <v>1118</v>
+      </c>
+      <c r="C1143" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1143" s="17" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="1144" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1144" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1144" s="17" t="s">
+        <v>1119</v>
+      </c>
+      <c r="C1144" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1144" s="17" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="1145" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1145" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1145" s="17" t="s">
+        <v>1120</v>
+      </c>
+      <c r="C1145" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1145" s="17" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="1146" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1146" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1146" s="17" t="s">
+        <v>1121</v>
+      </c>
+      <c r="C1146" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1146" s="17" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="1147" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1147" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1147" s="17" t="s">
+        <v>1122</v>
+      </c>
+      <c r="C1147" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1147" s="17" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="1148" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1148" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1148" s="17" t="s">
+        <v>1123</v>
+      </c>
+      <c r="C1148" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1148" s="17" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1149" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1149" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1149" s="17" t="s">
+        <v>1124</v>
+      </c>
+      <c r="C1149" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1149" s="17" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1150" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1150" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1150" s="17" t="s">
+        <v>1125</v>
+      </c>
+      <c r="C1150" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1150" s="17" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1151" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1151" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1151" s="17" t="s">
+        <v>1126</v>
+      </c>
+      <c r="C1151" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1151" s="17" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="1152" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1152" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1152" s="17" t="s">
+        <v>1127</v>
+      </c>
+      <c r="C1152" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1152" s="17" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="1153" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1153" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1153" s="17" t="s">
+        <v>1128</v>
+      </c>
+      <c r="C1153" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1153" s="17" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="1154" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1154" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1154" s="17" t="s">
+        <v>1129</v>
+      </c>
+      <c r="C1154" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1154" s="17" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="1155" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1155" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1155" s="17" t="s">
+        <v>1130</v>
+      </c>
+      <c r="C1155" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1155" s="17" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="1156" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1156" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1156" s="17" t="s">
+        <v>1131</v>
+      </c>
+      <c r="C1156" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1156" s="17" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="1157" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1157" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1157" s="17" t="s">
+        <v>1132</v>
+      </c>
+      <c r="C1157" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1157" s="17" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="1158" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1158" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1158" s="17" t="s">
+        <v>1133</v>
+      </c>
+      <c r="C1158" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1158" s="17" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="1159" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1159" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1159" s="17" t="s">
+        <v>1134</v>
+      </c>
+      <c r="C1159" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1159" s="17" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="1160" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1160" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1160" s="17" t="s">
+        <v>1135</v>
+      </c>
+      <c r="C1160" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1160" s="17" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="1161" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1161" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1161" s="17" t="s">
+        <v>1136</v>
+      </c>
+      <c r="C1161" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1161" s="17" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="1162" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1162" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1162" s="17" t="s">
+        <v>1137</v>
+      </c>
+      <c r="C1162" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1162" s="17" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="1163" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1163" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1163" s="17" t="s">
+        <v>1138</v>
+      </c>
+      <c r="C1163" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1163" s="17" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="1164" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1164" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1164" s="17" t="s">
+        <v>1139</v>
+      </c>
+      <c r="C1164" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1164" s="17" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="1165" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1165" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1165" s="17" t="s">
+        <v>1140</v>
+      </c>
+      <c r="C1165" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1165" s="17" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="1166" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1166" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1166" s="17" t="s">
+        <v>1141</v>
+      </c>
+      <c r="C1166" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1166" s="17" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="1167" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1167" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1167" s="17" t="s">
+        <v>1142</v>
+      </c>
+      <c r="C1167" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1167" s="17" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="1168" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1168" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1168" s="17" t="s">
+        <v>1143</v>
+      </c>
+      <c r="C1168" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1168" s="17" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="1169" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1169" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1169" s="17" t="s">
+        <v>1144</v>
+      </c>
+      <c r="C1169" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1169" s="17" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="1170" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1170" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1170" s="17" t="s">
+        <v>1145</v>
+      </c>
+      <c r="C1170" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1170" s="17" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="1171" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1171" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1171" s="17" t="s">
+        <v>1146</v>
+      </c>
+      <c r="C1171" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1171" s="17" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="1172" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1172" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1172" s="17" t="s">
+        <v>1147</v>
+      </c>
+      <c r="C1172" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1172" s="17" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="1173" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1173" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1173" s="17" t="s">
+        <v>1148</v>
+      </c>
+      <c r="C1173" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1173" s="17" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="1174" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1174" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1174" s="17" t="s">
+        <v>1149</v>
+      </c>
+      <c r="C1174" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1174" s="17" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="1175" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1175" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1175" s="17" t="s">
+        <v>1150</v>
+      </c>
+      <c r="C1175" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1175" s="17" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="1176" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1176" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1176" s="17" t="s">
+        <v>1151</v>
+      </c>
+      <c r="C1176" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1176" s="17" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="1177" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1177" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1177" s="17" t="s">
+        <v>1152</v>
+      </c>
+      <c r="C1177" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1177" s="17" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="1178" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1178" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1178" s="17" t="s">
+        <v>1153</v>
+      </c>
+      <c r="C1178" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1178" s="17" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="1179" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1179" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1179" s="17" t="s">
+        <v>1154</v>
+      </c>
+      <c r="C1179" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1179" s="17" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="1180" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1180" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1180" s="17" t="s">
+        <v>1155</v>
+      </c>
+      <c r="C1180" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1180" s="17" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="1181" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1181" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1181" s="17" t="s">
+        <v>1156</v>
+      </c>
+      <c r="C1181" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1181" s="17" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="1182" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1182" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1182" s="17" t="s">
+        <v>1157</v>
+      </c>
+      <c r="C1182" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1182" s="17" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="1183" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1183" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1183" s="17" t="s">
+        <v>1158</v>
+      </c>
+      <c r="C1183" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1183" s="17" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1184" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1184" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1184" s="17" t="s">
+        <v>1159</v>
+      </c>
+      <c r="C1184" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1184" s="17" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1185" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1185" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1185" s="17" t="s">
+        <v>1160</v>
+      </c>
+      <c r="C1185" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1185" s="17" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1186" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1186" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1186" s="17" t="s">
+        <v>1161</v>
+      </c>
+      <c r="C1186" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1186" s="17" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="1187" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1187" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1187" s="17" t="s">
+        <v>1162</v>
+      </c>
+      <c r="C1187" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1187" s="17" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="1188" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1188" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1188" s="17" t="s">
+        <v>1163</v>
+      </c>
+      <c r="C1188" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1188" s="17" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="1189" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1189" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1189" s="17" t="s">
+        <v>1164</v>
+      </c>
+      <c r="C1189" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1189" s="17" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1190" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1190" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1190" s="17" t="s">
+        <v>1165</v>
+      </c>
+      <c r="C1190" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1190" s="17" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1191" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1191" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1191" s="17" t="s">
+        <v>1166</v>
+      </c>
+      <c r="C1191" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1191" s="17" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1192" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1192" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1192" s="17" t="s">
+        <v>1167</v>
+      </c>
+      <c r="C1192" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1192" s="17" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1193" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1193" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1193" s="17" t="s">
+        <v>1168</v>
+      </c>
+      <c r="C1193" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1193" s="17" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="1194" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1194" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1194" s="17" t="s">
+        <v>1169</v>
+      </c>
+      <c r="C1194" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1194" s="17" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="1195" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1195" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1195" s="17" t="s">
+        <v>1170</v>
+      </c>
+      <c r="C1195" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1195" s="17" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="1196" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1196" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1196" s="17" t="s">
+        <v>1171</v>
+      </c>
+      <c r="C1196" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1196" s="17" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="1197" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1197" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1197" s="17" t="s">
+        <v>1172</v>
+      </c>
+      <c r="C1197" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1197" s="17" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="1198" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1198" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1198" s="17" t="s">
+        <v>1173</v>
+      </c>
+      <c r="C1198" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1198" s="17" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="1199" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1199" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1199" s="17" t="s">
+        <v>1174</v>
+      </c>
+      <c r="C1199" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1199" s="17" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="1200" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1200" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1200" s="17" t="s">
+        <v>1175</v>
+      </c>
+      <c r="C1200" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1200" s="17" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="1201" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1201" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1201" s="17" t="s">
+        <v>1176</v>
+      </c>
+      <c r="C1201" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1201" s="17" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="1202" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1202" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1202" s="17" t="s">
+        <v>1177</v>
+      </c>
+      <c r="C1202" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1202" s="17" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="1203" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1203" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1203" s="17" t="s">
+        <v>1178</v>
+      </c>
+      <c r="C1203" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1203" s="17" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="1204" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1204" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1204" s="17" t="s">
+        <v>1179</v>
+      </c>
+      <c r="C1204" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1204" s="17" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="1205" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1205" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1205" s="17" t="s">
+        <v>1180</v>
+      </c>
+      <c r="C1205" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1205" s="17" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="1206" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1206" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1206" s="17" t="s">
+        <v>1181</v>
+      </c>
+      <c r="C1206" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1206" s="17" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="1207" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1207" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1207" s="17" t="s">
+        <v>1182</v>
+      </c>
+      <c r="C1207" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1207" s="17" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="1208" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1208" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1208" s="17" t="s">
+        <v>1183</v>
+      </c>
+      <c r="C1208" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1208" s="17" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="1209" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1209" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1209" s="17" t="s">
+        <v>1184</v>
+      </c>
+      <c r="C1209" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1209" s="17" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="1210" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1210" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1210" s="17" t="s">
+        <v>1185</v>
+      </c>
+      <c r="C1210" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1210" s="17" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="1211" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1211" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1211" s="17" t="s">
+        <v>1186</v>
+      </c>
+      <c r="C1211" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1211" s="17" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="1212" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1212" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1212" s="17" t="s">
+        <v>1187</v>
+      </c>
+      <c r="C1212" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1212" s="17" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="1213" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1213" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1213" s="17" t="s">
+        <v>1188</v>
+      </c>
+      <c r="C1213" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1213" s="17" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="1214" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1214" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1214" s="17" t="s">
+        <v>1189</v>
+      </c>
+      <c r="C1214" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1214" s="17" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="1215" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1215" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1215" s="17" t="s">
+        <v>1190</v>
+      </c>
+      <c r="C1215" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1215" s="17" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="1216" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1216" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1216" s="17" t="s">
+        <v>1191</v>
+      </c>
+      <c r="C1216" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1216" s="17" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="1217" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1217" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1217" s="17" t="s">
+        <v>1192</v>
+      </c>
+      <c r="C1217" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1217" s="17" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="1218" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1218" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1218" s="17" t="s">
+        <v>1193</v>
+      </c>
+      <c r="C1218" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1218" s="17" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="1219" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1219" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1219" s="17" t="s">
+        <v>1194</v>
+      </c>
+      <c r="C1219" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1219" s="17" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="1220" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1220" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1220" s="17" t="s">
+        <v>1195</v>
+      </c>
+      <c r="C1220" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1220" s="17" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="1221" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1221" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1221" s="17" t="s">
+        <v>1196</v>
+      </c>
+      <c r="C1221" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1221" s="17" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="1222" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1222" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1222" s="17" t="s">
+        <v>1197</v>
+      </c>
+      <c r="C1222" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1222" s="17" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="1223" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1223" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1223" s="17" t="s">
+        <v>1198</v>
+      </c>
+      <c r="C1223" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1223" s="17" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="1224" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1224" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1224" s="17" t="s">
+        <v>1199</v>
+      </c>
+      <c r="C1224" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1224" s="17" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="1225" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1225" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1225" s="17" t="s">
+        <v>1200</v>
+      </c>
+      <c r="C1225" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1225" s="17" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="1226" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1226" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1226" s="17" t="s">
+        <v>1201</v>
+      </c>
+      <c r="C1226" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1226" s="17" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="1227" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1227" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1227" s="17" t="s">
+        <v>1202</v>
+      </c>
+      <c r="C1227" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1227" s="17" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="1228" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1228" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1228" s="17" t="s">
+        <v>1203</v>
+      </c>
+      <c r="C1228" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1228" s="17" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="1229" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1229" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1229" s="17" t="s">
+        <v>1204</v>
+      </c>
+      <c r="C1229" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1229" s="17" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="1230" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1230" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1230" s="17" t="s">
+        <v>1205</v>
+      </c>
+      <c r="C1230" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1230" s="17" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="1231" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1231" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1231" s="17" t="s">
+        <v>1206</v>
+      </c>
+      <c r="C1231" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1231" s="17" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="1232" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1232" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1232" s="17" t="s">
+        <v>1207</v>
+      </c>
+      <c r="C1232" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1232" s="17" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="1233" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1233" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1233" s="17" t="s">
+        <v>1208</v>
+      </c>
+      <c r="C1233" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1233" s="17" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="1234" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1234" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1234" s="17" t="s">
+        <v>1209</v>
+      </c>
+      <c r="C1234" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1234" s="17" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="1235" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1235" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1235" s="17" t="s">
+        <v>1210</v>
+      </c>
+      <c r="C1235" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1235" s="17" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="1236" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1236" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1236" s="17" t="s">
+        <v>1211</v>
+      </c>
+      <c r="C1236" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1236" s="17" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="1237" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1237" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1237" s="17" t="s">
+        <v>1212</v>
+      </c>
+      <c r="C1237" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1237" s="17" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="1238" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1238" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1238" s="17" t="s">
+        <v>1213</v>
+      </c>
+      <c r="C1238" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1238" s="17" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="1239" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1239" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1239" s="17" t="s">
+        <v>1214</v>
+      </c>
+      <c r="C1239" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1239" s="17" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="1240" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1240" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1240" s="17" t="s">
+        <v>1215</v>
+      </c>
+      <c r="C1240" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1240" s="17" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="1241" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1241" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1241" s="17" t="s">
+        <v>1216</v>
+      </c>
+      <c r="C1241" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1241" s="17" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="1242" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1242" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1242" s="17" t="s">
+        <v>1217</v>
+      </c>
+      <c r="C1242" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1242" s="17" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="1243" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1243" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1243" s="17" t="s">
+        <v>1218</v>
+      </c>
+      <c r="C1243" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1243" s="17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="1244" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1244" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1244" s="17" t="s">
+        <v>1219</v>
+      </c>
+      <c r="C1244" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1244" s="17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="1245" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1245" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1245" s="17" t="s">
+        <v>1220</v>
+      </c>
+      <c r="C1245" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1245" s="17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="1246" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1246" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1246" s="17" t="s">
+        <v>1221</v>
+      </c>
+      <c r="C1246" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1246" s="17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="1247" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1247" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1247" s="17" t="s">
+        <v>1222</v>
+      </c>
+      <c r="C1247" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1247" s="17" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="1248" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1248" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1248" s="17" t="s">
+        <v>1223</v>
+      </c>
+      <c r="C1248" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1248" s="17" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="1249" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1249" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1249" s="17" t="s">
+        <v>1224</v>
+      </c>
+      <c r="C1249" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1249" s="17" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="1250" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1250" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1250" s="17" t="s">
+        <v>1225</v>
+      </c>
+      <c r="C1250" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1250" s="17" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="1251" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1251" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1251" s="17" t="s">
+        <v>1226</v>
+      </c>
+      <c r="C1251" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1251" s="17" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="1252" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1252" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1252" s="17" t="s">
+        <v>1227</v>
+      </c>
+      <c r="C1252" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1252" s="17" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="1253" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1253" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1253" s="17" t="s">
+        <v>1228</v>
+      </c>
+      <c r="C1253" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1253" s="17" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="1254" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1254" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1254" s="17" t="s">
+        <v>1229</v>
+      </c>
+      <c r="C1254" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1254" s="17" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="1255" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1255" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1255" s="17" t="s">
+        <v>1230</v>
+      </c>
+      <c r="C1255" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1255" s="17" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="1256" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1256" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1256" s="17" t="s">
+        <v>1231</v>
+      </c>
+      <c r="C1256" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1256" s="17" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="1257" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1257" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1257" s="17" t="s">
+        <v>1232</v>
+      </c>
+      <c r="C1257" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1257" s="17" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="1258" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1258" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1258" s="17" t="s">
+        <v>1233</v>
+      </c>
+      <c r="C1258" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1258" s="17" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1259" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1259" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1259" s="17" t="s">
+        <v>1234</v>
+      </c>
+      <c r="C1259" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1259" s="17" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1260" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1260" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1260" s="17" t="s">
+        <v>1235</v>
+      </c>
+      <c r="C1260" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1260" s="17" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1261" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1261" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1261" s="17" t="s">
+        <v>1236</v>
+      </c>
+      <c r="C1261" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1261" s="17" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1262" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1262" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1262" s="17" t="s">
+        <v>1237</v>
+      </c>
+      <c r="C1262" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1262" s="17" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1263" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1263" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1263" s="17" t="s">
+        <v>1238</v>
+      </c>
+      <c r="C1263" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1263" s="17" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1264" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1264" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1264" s="17" t="s">
+        <v>1239</v>
+      </c>
+      <c r="C1264" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1264" s="17" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1265" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1265" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1265" s="17" t="s">
+        <v>1240</v>
+      </c>
+      <c r="C1265" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1265" s="17" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1266" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1266" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1266" s="17" t="s">
+        <v>1241</v>
+      </c>
+      <c r="C1266" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1266" s="17" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1267" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1267" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1267" s="17" t="s">
+        <v>1242</v>
+      </c>
+      <c r="C1267" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1267" s="17" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1268" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1268" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1268" s="17" t="s">
+        <v>1243</v>
+      </c>
+      <c r="C1268" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1268" s="17" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1269" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1269" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1269" s="17" t="s">
+        <v>1244</v>
+      </c>
+      <c r="C1269" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1269" s="17" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1270" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1270" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1270" s="17" t="s">
+        <v>1245</v>
+      </c>
+      <c r="C1270" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1270" s="17" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1271" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1271" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1271" s="17" t="s">
+        <v>1246</v>
+      </c>
+      <c r="C1271" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1271" s="17" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1272" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1272" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1272" s="17" t="s">
+        <v>1247</v>
+      </c>
+      <c r="C1272" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1272" s="17" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1273" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1273" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1273" s="17" t="s">
+        <v>1248</v>
+      </c>
+      <c r="C1273" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1273" s="17" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="1274" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1274" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1274" s="17" t="s">
+        <v>1249</v>
+      </c>
+      <c r="C1274" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1274" s="17" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="1275" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1275" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1275" s="17" t="s">
+        <v>1250</v>
+      </c>
+      <c r="C1275" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1275" s="17" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="1276" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1276" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1276" s="17" t="s">
+        <v>1251</v>
+      </c>
+      <c r="C1276" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1276" s="17" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="1277" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1277" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1277" s="17" t="s">
+        <v>1252</v>
+      </c>
+      <c r="C1277" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1277" s="17" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="1278" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1278" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1278" s="17" t="s">
+        <v>1253</v>
+      </c>
+      <c r="C1278" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1278" s="17" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="1279" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1279" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1279" s="17" t="s">
+        <v>1254</v>
+      </c>
+      <c r="C1279" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1279" s="17" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="1280" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1280" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1280" s="17" t="s">
+        <v>1255</v>
+      </c>
+      <c r="C1280" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1280" s="17" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="1281" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1281" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1281" s="17" t="s">
+        <v>1256</v>
+      </c>
+      <c r="C1281" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1281" s="17" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="1282" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1282" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1282" s="17" t="s">
+        <v>1257</v>
+      </c>
+      <c r="C1282" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1282" s="17" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="1283" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1283" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1283" s="17" t="s">
+        <v>1258</v>
+      </c>
+      <c r="C1283" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1283" s="17" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="1284" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1284" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1284" s="17" t="s">
+        <v>1259</v>
+      </c>
+      <c r="C1284" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1284" s="17" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="1285" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1285" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1285" s="17" t="s">
+        <v>1260</v>
+      </c>
+      <c r="C1285" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1285" s="17" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="1286" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1286" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1286" s="17" t="s">
+        <v>1261</v>
+      </c>
+      <c r="C1286" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1286" s="17" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="1287" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1287" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1287" s="17" t="s">
+        <v>1262</v>
+      </c>
+      <c r="C1287" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1287" s="17" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="1288" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1288" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1288" s="17" t="s">
+        <v>1263</v>
+      </c>
+      <c r="C1288" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1288" s="17" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="1289" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1289" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1289" s="17" t="s">
+        <v>1264</v>
+      </c>
+      <c r="C1289" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1289" s="17" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="1290" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1290" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1290" s="17" t="s">
+        <v>1265</v>
+      </c>
+      <c r="C1290" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1290" s="17" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="1291" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1291" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1291" s="17" t="s">
+        <v>1266</v>
+      </c>
+      <c r="C1291" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1291" s="17" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="1292" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1292" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1292" s="17" t="s">
+        <v>1267</v>
+      </c>
+      <c r="C1292" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1292" s="17" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="1293" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1293" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1293" s="17" t="s">
+        <v>1268</v>
+      </c>
+      <c r="C1293" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1293" s="17" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="1294" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1294" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1294" s="17" t="s">
+        <v>1269</v>
+      </c>
+      <c r="C1294" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1294" s="17" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="1295" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1295" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1295" s="17" t="s">
+        <v>1270</v>
+      </c>
+      <c r="C1295" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1295" s="17" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="1296" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1296" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1296" s="17" t="s">
+        <v>1271</v>
+      </c>
+      <c r="C1296" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1296" s="17" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="1297" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1297" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1297" s="17" t="s">
+        <v>1272</v>
+      </c>
+      <c r="C1297" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1297" s="17" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="1298" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1298" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1298" s="17" t="s">
+        <v>1273</v>
+      </c>
+      <c r="C1298" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1298" s="17" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="1299" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1299" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1299" s="17" t="s">
+        <v>1274</v>
+      </c>
+      <c r="C1299" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1299" s="17" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="1300" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1300" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1300" s="17" t="s">
+        <v>1275</v>
+      </c>
+      <c r="C1300" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1300" s="17" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="1301" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1301" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1301" s="17" t="s">
+        <v>1276</v>
+      </c>
+      <c r="C1301" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1301" s="17" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="1302" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1302" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1302" s="17" t="s">
+        <v>1277</v>
+      </c>
+      <c r="C1302" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1302" s="17" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="1303" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1303" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1303" s="17" t="s">
+        <v>1278</v>
+      </c>
+      <c r="C1303" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1303" s="17" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="1304" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1304" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1304" s="17" t="s">
+        <v>1279</v>
+      </c>
+      <c r="C1304" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1304" s="17" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="1305" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1305" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1305" s="17" t="s">
+        <v>1280</v>
+      </c>
+      <c r="C1305" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1305" s="17" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="1306" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1306" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1306" s="17" t="s">
+        <v>1281</v>
+      </c>
+      <c r="C1306" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1306" s="17" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="1307" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1307" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1307" s="17" t="s">
+        <v>1282</v>
+      </c>
+      <c r="C1307" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1307" s="17" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="1308" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1308" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1308" s="17" t="s">
+        <v>1283</v>
+      </c>
+      <c r="C1308" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1308" s="17" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="1309" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1309" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1309" s="17" t="s">
+        <v>1284</v>
+      </c>
+      <c r="C1309" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1309" s="17" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="1310" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1310" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1310" s="17" t="s">
+        <v>1285</v>
+      </c>
+      <c r="C1310" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1310" s="17" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="1311" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1311" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1311" s="17" t="s">
+        <v>1286</v>
+      </c>
+      <c r="C1311" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1311" s="17" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="1312" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1312" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1312" s="17" t="s">
+        <v>1287</v>
+      </c>
+      <c r="C1312" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1312" s="17" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="1313" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1313" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1313" s="17" t="s">
+        <v>1288</v>
+      </c>
+      <c r="C1313" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1313" s="17" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="1314" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1314" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1314" s="17" t="s">
+        <v>1289</v>
+      </c>
+      <c r="C1314" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1314" s="17" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="1315" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1315" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1315" s="17" t="s">
+        <v>1290</v>
+      </c>
+      <c r="C1315" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1315" s="17" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="1316" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1316" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1316" s="17" t="s">
+        <v>1291</v>
+      </c>
+      <c r="C1316" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1316" s="17" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="1317" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1317" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1317" s="17" t="s">
+        <v>1292</v>
+      </c>
+      <c r="C1317" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1317" s="17" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="1318" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1318" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1318" s="17" t="s">
+        <v>1293</v>
+      </c>
+      <c r="C1318" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1318" s="17" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="1319" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1319" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1319" s="17" t="s">
+        <v>1294</v>
+      </c>
+      <c r="C1319" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1319" s="17" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="1320" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1320" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1320" s="17" t="s">
+        <v>1295</v>
+      </c>
+      <c r="C1320" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1320" s="17" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="1321" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1321" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1321" s="17" t="s">
+        <v>1296</v>
+      </c>
+      <c r="C1321" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1321" s="17" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="1322" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1322" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1322" s="17" t="s">
+        <v>1297</v>
+      </c>
+      <c r="C1322" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1322" s="17" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="1323" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1323" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1323" s="17" t="s">
+        <v>1298</v>
+      </c>
+      <c r="C1323" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1323" s="17" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1324" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1324" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1324" s="17" t="s">
+        <v>1299</v>
+      </c>
+      <c r="C1324" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1324" s="17" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1325" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1325" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1325" s="17" t="s">
+        <v>1300</v>
+      </c>
+      <c r="C1325" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1325" s="17" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1326" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1326" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1326" s="17" t="s">
+        <v>1301</v>
+      </c>
+      <c r="C1326" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1326" s="17" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1327" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1327" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1327" s="17" t="s">
+        <v>1302</v>
+      </c>
+      <c r="C1327" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1327" s="17" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1328" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1328" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1328" s="17" t="s">
+        <v>1303</v>
+      </c>
+      <c r="C1328" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1328" s="17" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1329" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1329" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1329" s="17" t="s">
+        <v>1304</v>
+      </c>
+      <c r="C1329" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1329" s="17" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1330" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1330" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1330" s="17" t="s">
+        <v>1305</v>
+      </c>
+      <c r="C1330" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1330" s="17" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1331" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1331" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1331" s="17" t="s">
+        <v>1306</v>
+      </c>
+      <c r="C1331" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1331" s="17" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1332" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1332" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1332" s="17" t="s">
+        <v>1307</v>
+      </c>
+      <c r="C1332" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1332" s="17" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="1333" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1333" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1333" s="17" t="s">
+        <v>1308</v>
+      </c>
+      <c r="C1333" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1333" s="17" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="1334" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1334" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1334" s="17" t="s">
+        <v>1309</v>
+      </c>
+      <c r="C1334" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1334" s="17" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="1335" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1335" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1335" s="17" t="s">
+        <v>1310</v>
+      </c>
+      <c r="C1335" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1335" s="17" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="1336" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1336" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1336" s="17" t="s">
+        <v>1311</v>
+      </c>
+      <c r="C1336" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1336" s="17" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="1337" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1337" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1337" s="17" t="s">
+        <v>1312</v>
+      </c>
+      <c r="C1337" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1337" s="17" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="1338" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1338" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1338" s="17" t="s">
+        <v>1313</v>
+      </c>
+      <c r="C1338" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1338" s="17" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="1339" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1339" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1339" s="17" t="s">
+        <v>1314</v>
+      </c>
+      <c r="C1339" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1339" s="17" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="1340" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1340" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1340" s="17" t="s">
+        <v>1315</v>
+      </c>
+      <c r="C1340" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1340" s="17" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="1341" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1341" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1341" s="17" t="s">
+        <v>1316</v>
+      </c>
+      <c r="C1341" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1341" s="17" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="1342" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1342" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1342" s="17" t="s">
+        <v>1317</v>
+      </c>
+      <c r="C1342" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1342" s="17" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="1343" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1343" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1343" s="17" t="s">
+        <v>1318</v>
+      </c>
+      <c r="C1343" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1343" s="17" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="1344" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1344" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1344" s="17" t="s">
+        <v>1319</v>
+      </c>
+      <c r="C1344" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1344" s="17" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="1345" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1345" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1345" s="17" t="s">
+        <v>1320</v>
+      </c>
+      <c r="C1345" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1345" s="17" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="1346" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1346" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1346" s="17" t="s">
+        <v>1321</v>
+      </c>
+      <c r="C1346" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1346" s="17" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="1347" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1347" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1347" s="17" t="s">
+        <v>1322</v>
+      </c>
+      <c r="C1347" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1347" s="17" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="1348" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1348" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1348" s="17" t="s">
+        <v>1323</v>
+      </c>
+      <c r="C1348" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1348" s="17" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="1349" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1349" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1349" s="17" t="s">
+        <v>1324</v>
+      </c>
+      <c r="C1349" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1349" s="17" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="1350" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1350" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1350" s="17" t="s">
+        <v>1325</v>
+      </c>
+      <c r="C1350" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1350" s="17" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="1351" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1351" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1351" s="17" t="s">
+        <v>1326</v>
+      </c>
+      <c r="C1351" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1351" s="17" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="1352" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1352" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1352" s="17" t="s">
+        <v>1327</v>
+      </c>
+      <c r="C1352" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1352" s="17" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="1353" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1353" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1353" s="17" t="s">
+        <v>1328</v>
+      </c>
+      <c r="C1353" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1353" s="17" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1354" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1354" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1354" s="17" t="s">
+        <v>1329</v>
+      </c>
+      <c r="C1354" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1354" s="17" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1355" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1355" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1355" s="17" t="s">
+        <v>1330</v>
+      </c>
+      <c r="C1355" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1355" s="17" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1356" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1356" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1356" s="17" t="s">
+        <v>1331</v>
+      </c>
+      <c r="C1356" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1356" s="17" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1357" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1357" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1357" s="17" t="s">
+        <v>1332</v>
+      </c>
+      <c r="C1357" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1357" s="17" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1358" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1358" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1358" s="17" t="s">
+        <v>1333</v>
+      </c>
+      <c r="C1358" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1358" s="17" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1359" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1359" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1359" s="17" t="s">
+        <v>1334</v>
+      </c>
+      <c r="C1359" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1359" s="17" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1360" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1360" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1360" s="17" t="s">
+        <v>1335</v>
+      </c>
+      <c r="C1360" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1360" s="17" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1361" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1361" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1361" s="17" t="s">
+        <v>1336</v>
+      </c>
+      <c r="C1361" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1361" s="17" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1362" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1362" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1362" s="17" t="s">
+        <v>1337</v>
+      </c>
+      <c r="C1362" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1362" s="17" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1363" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1363" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1363" s="17" t="s">
+        <v>1338</v>
+      </c>
+      <c r="C1363" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1363" s="17" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1364" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1364" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1364" s="17" t="s">
+        <v>1339</v>
+      </c>
+      <c r="C1364" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1364" s="17" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1365" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1365" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1365" s="17" t="s">
+        <v>1340</v>
+      </c>
+      <c r="C1365" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1365" s="17" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1366" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1366" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1366" s="17" t="s">
+        <v>1341</v>
+      </c>
+      <c r="C1366" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1366" s="17" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1367" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1367" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1367" s="17" t="s">
+        <v>1342</v>
+      </c>
+      <c r="C1367" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1367" s="17" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1368" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1368" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1368" s="17" t="s">
+        <v>1343</v>
+      </c>
+      <c r="C1368" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1368" s="17" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="1369" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1369" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1369" s="17" t="s">
+        <v>1344</v>
+      </c>
+      <c r="C1369" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1369" s="17" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="1370" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1370" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1370" s="17" t="s">
+        <v>1345</v>
+      </c>
+      <c r="C1370" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1370" s="17" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="1371" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1371" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1371" s="17" t="s">
+        <v>1346</v>
+      </c>
+      <c r="C1371" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1371" s="17" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="1372" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1372" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1372" s="17" t="s">
+        <v>1347</v>
+      </c>
+      <c r="C1372" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1372" s="17" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="1373" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1373" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1373" s="17" t="s">
+        <v>1348</v>
+      </c>
+      <c r="C1373" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1373" s="17" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="1374" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1374" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1374" s="17" t="s">
+        <v>1349</v>
+      </c>
+      <c r="C1374" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1374" s="17" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="1375" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1375" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1375" s="17" t="s">
+        <v>1350</v>
+      </c>
+      <c r="C1375" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1375" s="17" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="1376" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1376" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1376" s="17" t="s">
+        <v>1351</v>
+      </c>
+      <c r="C1376" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1376" s="17" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="1377" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1377" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1377" s="17" t="s">
+        <v>1352</v>
+      </c>
+      <c r="C1377" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1377" s="17" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="1378" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1378" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1378" s="17" t="s">
+        <v>1353</v>
+      </c>
+      <c r="C1378" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1378" s="17" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="1379" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1379" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1379" s="17" t="s">
+        <v>1354</v>
+      </c>
+      <c r="C1379" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1379" s="17" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="1380" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1380" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1380" s="17" t="s">
+        <v>1355</v>
+      </c>
+      <c r="C1380" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1380" s="17" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="1381" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1381" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1381" s="17" t="s">
+        <v>1356</v>
+      </c>
+      <c r="C1381" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1381" s="17" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="1382" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1382" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1382" s="17" t="s">
+        <v>1357</v>
+      </c>
+      <c r="C1382" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1382" s="17" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="1383" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1383" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1383" s="17" t="s">
+        <v>1358</v>
+      </c>
+      <c r="C1383" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1383" s="17" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="1384" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1384" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1384" s="17" t="s">
+        <v>1359</v>
+      </c>
+      <c r="C1384" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1384" s="17" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="1385" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1385" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1385" s="17" t="s">
+        <v>1360</v>
+      </c>
+      <c r="C1385" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1385" s="17" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="1386" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1386" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1386" s="17" t="s">
+        <v>1361</v>
+      </c>
+      <c r="C1386" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1386" s="17" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="1387" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1387" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1387" s="17" t="s">
+        <v>1362</v>
+      </c>
+      <c r="C1387" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1387" s="17" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="1388" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1388" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1388" s="17" t="s">
+        <v>1363</v>
+      </c>
+      <c r="C1388" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1388" s="17" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="1389" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1389" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1389" s="17" t="s">
+        <v>1364</v>
+      </c>
+      <c r="C1389" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1389" s="17" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="1390" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1390" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1390" s="17" t="s">
+        <v>1365</v>
+      </c>
+      <c r="C1390" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1390" s="17" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="1391" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1391" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1391" s="17" t="s">
+        <v>1366</v>
+      </c>
+      <c r="C1391" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1391" s="17" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="1392" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1392" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1392" s="17" t="s">
+        <v>1367</v>
+      </c>
+      <c r="C1392" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1392" s="17" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="1393" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1393" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1393" s="17" t="s">
+        <v>1368</v>
+      </c>
+      <c r="C1393" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1393" s="17" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="1394" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1394" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1394" s="17" t="s">
+        <v>1369</v>
+      </c>
+      <c r="C1394" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1394" s="17" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="1395" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1395" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1395" s="17" t="s">
+        <v>1370</v>
+      </c>
+      <c r="C1395" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1395" s="17" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="1396" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1396" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1396" s="17" t="s">
+        <v>1371</v>
+      </c>
+      <c r="C1396" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1396" s="17" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="1397" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1397" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1397" s="17" t="s">
+        <v>1372</v>
+      </c>
+      <c r="C1397" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1397" s="17" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="1398" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1398" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1398" s="17" t="s">
+        <v>1373</v>
+      </c>
+      <c r="C1398" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1398" s="17" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="1399" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1399" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1399" s="17" t="s">
+        <v>1374</v>
+      </c>
+      <c r="C1399" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1399" s="17" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="1400" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1400" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1400" s="17" t="s">
+        <v>1375</v>
+      </c>
+      <c r="C1400" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1400" s="17" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="1401" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1401" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1401" s="17" t="s">
+        <v>1376</v>
+      </c>
+      <c r="C1401" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1401" s="17" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="1402" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1402" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1402" s="17" t="s">
+        <v>1377</v>
+      </c>
+      <c r="C1402" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1402" s="17" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="1403" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1403" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1403" s="17" t="s">
+        <v>1378</v>
+      </c>
+      <c r="C1403" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1403" s="17" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="1404" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1404" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1404" s="17" t="s">
+        <v>1379</v>
+      </c>
+      <c r="C1404" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1404" s="17" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="1405" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1405" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1405" s="17" t="s">
+        <v>1380</v>
+      </c>
+      <c r="C1405" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1405" s="17" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="1406" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1406" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1406" s="17" t="s">
+        <v>1381</v>
+      </c>
+      <c r="C1406" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1406" s="17" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="1407" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1407" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1407" s="17" t="s">
+        <v>1382</v>
+      </c>
+      <c r="C1407" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1407" s="17" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="1408" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1408" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1408" s="17" t="s">
+        <v>1383</v>
+      </c>
+      <c r="C1408" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1408" s="17" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="1409" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1409" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1409" s="17" t="s">
+        <v>1384</v>
+      </c>
+      <c r="C1409" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1409" s="17" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="1410" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1410" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1410" s="17" t="s">
+        <v>1385</v>
+      </c>
+      <c r="C1410" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1410" s="17" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="1411" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1411" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1411" s="17" t="s">
+        <v>1386</v>
+      </c>
+      <c r="C1411" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1411" s="17" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="1412" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1412" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1412" s="17" t="s">
+        <v>1387</v>
+      </c>
+      <c r="C1412" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1412" s="17" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="1413" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1413" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1413" s="17" t="s">
+        <v>1388</v>
+      </c>
+      <c r="C1413" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1413" s="17" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="1414" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1414" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1414" s="17" t="s">
+        <v>1389</v>
+      </c>
+      <c r="C1414" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1414" s="17" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="1415" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1415" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1415" s="17" t="s">
+        <v>1390</v>
+      </c>
+      <c r="C1415" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1415" s="17" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="1416" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1416" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1416" s="17" t="s">
+        <v>1391</v>
+      </c>
+      <c r="C1416" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1416" s="17" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="1417" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1417" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1417" s="17" t="s">
+        <v>1392</v>
+      </c>
+      <c r="C1417" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1417" s="17" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="1418" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1418" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1418" s="17" t="s">
+        <v>1393</v>
+      </c>
+      <c r="C1418" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1418" s="17" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="1419" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1419" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1419" s="17" t="s">
+        <v>1394</v>
+      </c>
+      <c r="C1419" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1419" s="17" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="1420" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1420" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1420" s="17" t="s">
+        <v>1395</v>
+      </c>
+      <c r="C1420" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1420" s="17" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="1421" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1421" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1421" s="17" t="s">
+        <v>1396</v>
+      </c>
+      <c r="C1421" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1421" s="17" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="1422" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1422" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1422" s="17" t="s">
+        <v>1397</v>
+      </c>
+      <c r="C1422" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1422" s="17" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="1423" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1423" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1423" s="17" t="s">
+        <v>1398</v>
+      </c>
+      <c r="C1423" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1423" s="17" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="1424" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1424" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1424" s="17" t="s">
+        <v>1399</v>
+      </c>
+      <c r="C1424" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1424" s="17" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="1425" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1425" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1425" s="17" t="s">
+        <v>1400</v>
+      </c>
+      <c r="C1425" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1425" s="17" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="1426" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1426" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1426" s="17" t="s">
+        <v>1401</v>
+      </c>
+      <c r="C1426" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1426" s="17" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="1427" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1427" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1427" s="17" t="s">
+        <v>1402</v>
+      </c>
+      <c r="C1427" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1427" s="17" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="1428" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1428" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1428" s="17" t="s">
+        <v>1403</v>
+      </c>
+      <c r="C1428" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1428" s="17" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="1429" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1429" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1429" s="17" t="s">
+        <v>1404</v>
+      </c>
+      <c r="C1429" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1429" s="17" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="1430" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1430" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1430" s="17" t="s">
+        <v>1405</v>
+      </c>
+      <c r="C1430" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1430" s="17" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="1431" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1431" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1431" s="17" t="s">
+        <v>1406</v>
+      </c>
+      <c r="C1431" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1431" s="17" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="1432" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1432" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1432" s="17" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C1432" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1432" s="17" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="1433" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1433" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1433" s="17" t="s">
+        <v>1408</v>
+      </c>
+      <c r="C1433" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1433" s="17" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="1434" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1434" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1434" s="17" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1434" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1434" s="17" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="1435" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1435" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1435" s="17" t="s">
+        <v>1410</v>
+      </c>
+      <c r="C1435" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1435" s="17" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="1436" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1436" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1436" s="17" t="s">
+        <v>1411</v>
+      </c>
+      <c r="C1436" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1436" s="17" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="1437" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1437" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1437" s="17" t="s">
+        <v>1412</v>
+      </c>
+      <c r="C1437" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1437" s="17" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="1438" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1438" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1438" s="17" t="s">
+        <v>1413</v>
+      </c>
+      <c r="C1438" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1438" s="17" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="1439" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1439" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1439" s="17" t="s">
+        <v>1414</v>
+      </c>
+      <c r="C1439" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1439" s="17" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="1440" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1440" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1440" s="17" t="s">
+        <v>1415</v>
+      </c>
+      <c r="C1440" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1440" s="17" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="1441" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1441" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1441" s="17" t="s">
+        <v>1416</v>
+      </c>
+      <c r="C1441" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1441" s="17" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="1442" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1442" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1442" s="17" t="s">
+        <v>1417</v>
+      </c>
+      <c r="C1442" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1442" s="17" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="1443" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1443" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1443" s="17" t="s">
+        <v>1418</v>
+      </c>
+      <c r="C1443" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1443" s="17" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="1444" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1444" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1444" s="17" t="s">
+        <v>1419</v>
+      </c>
+      <c r="C1444" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1444" s="17" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="1445" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1445" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1445" s="17" t="s">
+        <v>1420</v>
+      </c>
+      <c r="C1445" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1445" s="17" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="1446" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1446" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1446" s="17" t="s">
+        <v>1421</v>
+      </c>
+      <c r="C1446" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1446" s="17" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="1447" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1447" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1447" s="17" t="s">
+        <v>1422</v>
+      </c>
+      <c r="C1447" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1447" s="17" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="1448" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1448" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1448" s="17" t="s">
+        <v>1423</v>
+      </c>
+      <c r="C1448" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1448" s="17" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="1449" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1449" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1449" s="17" t="s">
+        <v>1424</v>
+      </c>
+      <c r="C1449" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1449" s="17" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="1450" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1450" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1450" s="17" t="s">
+        <v>1425</v>
+      </c>
+      <c r="C1450" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1450" s="17" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="1451" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1451" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1451" s="17" t="s">
+        <v>1426</v>
+      </c>
+      <c r="C1451" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1451" s="17" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="1452" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1452" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1452" s="17" t="s">
+        <v>1427</v>
+      </c>
+      <c r="C1452" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1452" s="17" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="1453" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1453" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1453" s="17" t="s">
+        <v>1428</v>
+      </c>
+      <c r="C1453" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1453" s="17" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="1454" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1454" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1454" s="17" t="s">
+        <v>1429</v>
+      </c>
+      <c r="C1454" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1454" s="17" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -19255,11 +27002,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A12">
-    <cfRule type="containsText" dxfId="167" priority="239" operator="containsText" text="RSE">
+    <cfRule type="containsText" dxfId="167" priority="238" operator="containsText" text="VACANT">
+      <formula>NOT(ISERROR(SEARCH("VACANT",A12)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="166" priority="239" operator="containsText" text="RSE">
       <formula>NOT(ISERROR(SEARCH("RSE",A12)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="166" priority="238" operator="containsText" text="VACANT">
-      <formula>NOT(ISERROR(SEARCH("VACANT",A12)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="165" priority="240" operator="containsText" text="CSE">
       <formula>NOT(ISERROR(SEARCH("CSE",A12)))</formula>
@@ -19279,14 +27026,14 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A18 A38">
-    <cfRule type="containsText" dxfId="161" priority="251" operator="containsText" text="CSE">
-      <formula>NOT(ISERROR(SEARCH("CSE",A18)))</formula>
+    <cfRule type="containsText" dxfId="161" priority="249" operator="containsText" text="VACANT">
+      <formula>NOT(ISERROR(SEARCH("VACANT",A18)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="160" priority="250" operator="containsText" text="RSE">
       <formula>NOT(ISERROR(SEARCH("RSE",A18)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="159" priority="249" operator="containsText" text="VACANT">
-      <formula>NOT(ISERROR(SEARCH("VACANT",A18)))</formula>
+    <cfRule type="containsText" dxfId="159" priority="251" operator="containsText" text="CSE">
+      <formula>NOT(ISERROR(SEARCH("CSE",A18)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A23">
@@ -19334,11 +27081,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A34">
-    <cfRule type="containsText" dxfId="148" priority="234" operator="containsText" text="RSE">
+    <cfRule type="containsText" dxfId="148" priority="233" operator="containsText" text="VACANT">
+      <formula>NOT(ISERROR(SEARCH("VACANT",A34)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="147" priority="234" operator="containsText" text="RSE">
       <formula>NOT(ISERROR(SEARCH("RSE",A34)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="147" priority="233" operator="containsText" text="VACANT">
-      <formula>NOT(ISERROR(SEARCH("VACANT",A34)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="146" priority="235" operator="containsText" text="CSE">
       <formula>NOT(ISERROR(SEARCH("CSE",A34)))</formula>
@@ -19361,14 +27108,14 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A36">
-    <cfRule type="containsText" dxfId="141" priority="221" operator="containsText" text="RSE">
+    <cfRule type="containsText" dxfId="141" priority="220" operator="containsText" text="VACANT">
+      <formula>NOT(ISERROR(SEARCH("VACANT",A36)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="140" priority="221" operator="containsText" text="RSE">
       <formula>NOT(ISERROR(SEARCH("RSE",A36)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="140" priority="222" operator="containsText" text="CSE">
+    <cfRule type="containsText" dxfId="139" priority="222" operator="containsText" text="CSE">
       <formula>NOT(ISERROR(SEARCH("CSE",A36)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="139" priority="220" operator="containsText" text="VACANT">
-      <formula>NOT(ISERROR(SEARCH("VACANT",A36)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A36:A48 A2:A14">
@@ -19382,42 +27129,42 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A41">
-    <cfRule type="containsText" dxfId="136" priority="232" operator="containsText" text="CSE">
-      <formula>NOT(ISERROR(SEARCH("CSE",A41)))</formula>
+    <cfRule type="containsText" dxfId="136" priority="229" operator="containsText" text="vacant">
+      <formula>NOT(ISERROR(SEARCH("vacant",A41)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="135" priority="230" operator="containsText" text="VACANT">
       <formula>NOT(ISERROR(SEARCH("VACANT",A41)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="134" priority="229" operator="containsText" text="vacant">
-      <formula>NOT(ISERROR(SEARCH("vacant",A41)))</formula>
+    <cfRule type="containsText" dxfId="134" priority="231" operator="containsText" text="RSE">
+      <formula>NOT(ISERROR(SEARCH("RSE",A41)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="133" priority="231" operator="containsText" text="RSE">
-      <formula>NOT(ISERROR(SEARCH("RSE",A41)))</formula>
+    <cfRule type="containsText" dxfId="133" priority="232" operator="containsText" text="CSE">
+      <formula>NOT(ISERROR(SEARCH("CSE",A41)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A45">
-    <cfRule type="containsText" dxfId="132" priority="242" operator="containsText" text="RSE">
+    <cfRule type="containsText" dxfId="132" priority="241" operator="containsText" text="VACANT">
+      <formula>NOT(ISERROR(SEARCH("VACANT",A45)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="131" priority="242" operator="containsText" text="RSE">
       <formula>NOT(ISERROR(SEARCH("RSE",A45)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="131" priority="241" operator="containsText" text="VACANT">
-      <formula>NOT(ISERROR(SEARCH("VACANT",A45)))</formula>
+    <cfRule type="containsText" dxfId="130" priority="243" operator="containsText" text="CSE">
+      <formula>NOT(ISERROR(SEARCH("CSE",A45)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="130" priority="247" operator="containsText" text="RSE">
+    <cfRule type="containsText" dxfId="129" priority="247" operator="containsText" text="RSE">
       <formula>NOT(ISERROR(SEARCH("RSE",A45)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="129" priority="243" operator="containsText" text="CSE">
-      <formula>NOT(ISERROR(SEARCH("CSE",A45)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="128" priority="248" operator="containsText" text="CSE">
       <formula>NOT(ISERROR(SEARCH("CSE",A45)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A49">
-    <cfRule type="containsText" dxfId="127" priority="202" operator="containsText" text="CSE">
+    <cfRule type="containsText" dxfId="127" priority="201" operator="containsText" text="RSE">
+      <formula>NOT(ISERROR(SEARCH("RSE",A49)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="126" priority="202" operator="containsText" text="CSE">
       <formula>NOT(ISERROR(SEARCH("CSE",A49)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="126" priority="201" operator="containsText" text="RSE">
-      <formula>NOT(ISERROR(SEARCH("RSE",A49)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A49:A50">
@@ -19431,17 +27178,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A51">
-    <cfRule type="containsText" dxfId="123" priority="227" operator="containsText" text="RSE">
-      <formula>NOT(ISERROR(SEARCH("RSE",A51)))</formula>
+    <cfRule type="containsText" dxfId="123" priority="197" operator="containsText" text="VACANT">
+      <formula>NOT(ISERROR(SEARCH("VACANT",A51)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="122" priority="226" operator="containsText" text="VACANT">
       <formula>NOT(ISERROR(SEARCH("VACANT",A51)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="121" priority="228" operator="containsText" text="CSE">
+    <cfRule type="containsText" dxfId="121" priority="227" operator="containsText" text="RSE">
+      <formula>NOT(ISERROR(SEARCH("RSE",A51)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="120" priority="228" operator="containsText" text="CSE">
       <formula>NOT(ISERROR(SEARCH("CSE",A51)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="120" priority="197" operator="containsText" text="VACANT">
-      <formula>NOT(ISERROR(SEARCH("VACANT",A51)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A51:A70">
@@ -19471,42 +27218,42 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A71:A88 A91:A115 A117:A120 A122:A140">
-    <cfRule type="containsText" dxfId="113" priority="125" operator="containsText" text="CSE">
+    <cfRule type="containsText" dxfId="113" priority="124" operator="containsText" text="RSE">
+      <formula>NOT(ISERROR(SEARCH("RSE",A71)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="112" priority="125" operator="containsText" text="CSE">
       <formula>NOT(ISERROR(SEARCH("CSE",A71)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="112" priority="124" operator="containsText" text="RSE">
-      <formula>NOT(ISERROR(SEARCH("RSE",A71)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A72">
-    <cfRule type="containsText" dxfId="111" priority="48" operator="containsText" text="vacant">
+    <cfRule type="containsText" dxfId="111" priority="41" operator="containsText" text="vacant">
       <formula>NOT(ISERROR(SEARCH("vacant",A72)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="110" priority="49" operator="containsText" text="RSE">
+    <cfRule type="containsText" dxfId="110" priority="42" operator="containsText" text="RSE">
       <formula>NOT(ISERROR(SEARCH("RSE",A72)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="109" priority="50" operator="containsText" text="CSE">
+    <cfRule type="containsText" dxfId="109" priority="43" operator="containsText" text="CSE">
       <formula>NOT(ISERROR(SEARCH("CSE",A72)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="108" priority="41" operator="containsText" text="vacant">
+    <cfRule type="containsText" dxfId="108" priority="44" operator="containsText" text="RSE">
+      <formula>NOT(ISERROR(SEARCH("RSE",A72)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="107" priority="45" operator="containsText" text="CSE">
+      <formula>NOT(ISERROR(SEARCH("CSE",A72)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="106" priority="46" operator="containsText" text="RSE">
+      <formula>NOT(ISERROR(SEARCH("RSE",A72)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="105" priority="47" operator="containsText" text="CSE">
+      <formula>NOT(ISERROR(SEARCH("CSE",A72)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="104" priority="48" operator="containsText" text="vacant">
       <formula>NOT(ISERROR(SEARCH("vacant",A72)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="107" priority="42" operator="containsText" text="RSE">
+    <cfRule type="containsText" dxfId="103" priority="49" operator="containsText" text="RSE">
       <formula>NOT(ISERROR(SEARCH("RSE",A72)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="106" priority="43" operator="containsText" text="CSE">
-      <formula>NOT(ISERROR(SEARCH("CSE",A72)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="105" priority="44" operator="containsText" text="RSE">
-      <formula>NOT(ISERROR(SEARCH("RSE",A72)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="104" priority="45" operator="containsText" text="CSE">
-      <formula>NOT(ISERROR(SEARCH("CSE",A72)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="103" priority="46" operator="containsText" text="RSE">
-      <formula>NOT(ISERROR(SEARCH("RSE",A72)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="102" priority="47" operator="containsText" text="CSE">
+    <cfRule type="containsText" dxfId="102" priority="50" operator="containsText" text="CSE">
       <formula>NOT(ISERROR(SEARCH("CSE",A72)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -19524,20 +27271,20 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A81">
-    <cfRule type="containsText" dxfId="98" priority="39" operator="containsText" text="RSE">
+    <cfRule type="containsText" dxfId="98" priority="35" operator="containsText" text="RSE">
       <formula>NOT(ISERROR(SEARCH("RSE",A81)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="97" priority="35" operator="containsText" text="RSE">
+    <cfRule type="containsText" dxfId="97" priority="36" operator="containsText" text="CSE">
+      <formula>NOT(ISERROR(SEARCH("CSE",A81)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="96" priority="37" operator="containsText" text="RSE">
       <formula>NOT(ISERROR(SEARCH("RSE",A81)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="96" priority="36" operator="containsText" text="CSE">
+    <cfRule type="containsText" dxfId="95" priority="38" operator="containsText" text="CSE">
       <formula>NOT(ISERROR(SEARCH("CSE",A81)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="95" priority="37" operator="containsText" text="RSE">
+    <cfRule type="containsText" dxfId="94" priority="39" operator="containsText" text="RSE">
       <formula>NOT(ISERROR(SEARCH("RSE",A81)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="94" priority="38" operator="containsText" text="CSE">
-      <formula>NOT(ISERROR(SEARCH("CSE",A81)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="93" priority="40" operator="containsText" text="CSE">
       <formula>NOT(ISERROR(SEARCH("CSE",A81)))</formula>
@@ -19572,31 +27319,31 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A83">
-    <cfRule type="containsText" dxfId="86" priority="72" operator="containsText" text="CSE">
+    <cfRule type="containsText" dxfId="86" priority="71" operator="containsText" text="RSE">
+      <formula>NOT(ISERROR(SEARCH("RSE",A83)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="85" priority="72" operator="containsText" text="CSE">
       <formula>NOT(ISERROR(SEARCH("CSE",A83)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="85" priority="71" operator="containsText" text="RSE">
-      <formula>NOT(ISERROR(SEARCH("RSE",A83)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A85">
-    <cfRule type="containsText" dxfId="84" priority="109" operator="containsText" text="RSE">
+    <cfRule type="containsText" dxfId="84" priority="89" operator="containsText" text="RSE">
       <formula>NOT(ISERROR(SEARCH("RSE",A85)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="83" priority="108" operator="containsText" text="CSE">
+    <cfRule type="containsText" dxfId="83" priority="90" operator="containsText" text="CSE">
       <formula>NOT(ISERROR(SEARCH("CSE",A85)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="82" priority="107" operator="containsText" text="RSE">
       <formula>NOT(ISERROR(SEARCH("RSE",A85)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="81" priority="90" operator="containsText" text="CSE">
+    <cfRule type="containsText" dxfId="81" priority="108" operator="containsText" text="CSE">
       <formula>NOT(ISERROR(SEARCH("CSE",A85)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="80" priority="110" operator="containsText" text="CSE">
+    <cfRule type="containsText" dxfId="80" priority="109" operator="containsText" text="RSE">
+      <formula>NOT(ISERROR(SEARCH("RSE",A85)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="79" priority="110" operator="containsText" text="CSE">
       <formula>NOT(ISERROR(SEARCH("CSE",A85)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="79" priority="89" operator="containsText" text="RSE">
-      <formula>NOT(ISERROR(SEARCH("RSE",A85)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A85:A86">
@@ -19626,26 +27373,26 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A88">
-    <cfRule type="containsText" dxfId="72" priority="55" operator="containsText" text="RSE">
+    <cfRule type="containsText" dxfId="72" priority="51" operator="containsText" text="RSE">
       <formula>NOT(ISERROR(SEARCH("RSE",A88)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="71" priority="56" operator="containsText" text="CSE">
+    <cfRule type="containsText" dxfId="71" priority="52" operator="containsText" text="CSE">
       <formula>NOT(ISERROR(SEARCH("CSE",A88)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="70" priority="53" operator="containsText" text="RSE">
       <formula>NOT(ISERROR(SEARCH("RSE",A88)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="69" priority="52" operator="containsText" text="CSE">
+    <cfRule type="containsText" dxfId="69" priority="54" operator="containsText" text="CSE">
       <formula>NOT(ISERROR(SEARCH("CSE",A88)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="68" priority="51" operator="containsText" text="RSE">
+    <cfRule type="containsText" dxfId="68" priority="55" operator="containsText" text="RSE">
       <formula>NOT(ISERROR(SEARCH("RSE",A88)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="67" priority="57" operator="containsText" text="RSE">
+    <cfRule type="containsText" dxfId="67" priority="56" operator="containsText" text="CSE">
+      <formula>NOT(ISERROR(SEARCH("CSE",A88)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="66" priority="57" operator="containsText" text="RSE">
       <formula>NOT(ISERROR(SEARCH("RSE",A88)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="66" priority="54" operator="containsText" text="CSE">
-      <formula>NOT(ISERROR(SEARCH("CSE",A88)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="65" priority="58" operator="containsText" text="CSE">
       <formula>NOT(ISERROR(SEARCH("CSE",A88)))</formula>
@@ -19683,31 +27430,31 @@
     <cfRule type="containsText" dxfId="58" priority="87" operator="containsText" text="RSE">
       <formula>NOT(ISERROR(SEARCH("RSE",A92)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="57" priority="103" operator="containsText" text="RSE">
+    <cfRule type="containsText" dxfId="57" priority="88" operator="containsText" text="CSE">
+      <formula>NOT(ISERROR(SEARCH("CSE",A92)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="56" priority="103" operator="containsText" text="RSE">
       <formula>NOT(ISERROR(SEARCH("RSE",A92)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="56" priority="104" operator="containsText" text="CSE">
-      <formula>NOT(ISERROR(SEARCH("CSE",A92)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="55" priority="88" operator="containsText" text="CSE">
+    <cfRule type="containsText" dxfId="55" priority="104" operator="containsText" text="CSE">
       <formula>NOT(ISERROR(SEARCH("CSE",A92)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A95">
-    <cfRule type="containsText" dxfId="54" priority="63" operator="containsText" text="vacant">
+    <cfRule type="containsText" dxfId="54" priority="61" operator="containsText" text="RSE">
+      <formula>NOT(ISERROR(SEARCH("RSE",A95)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="53" priority="62" operator="containsText" text="CSE">
+      <formula>NOT(ISERROR(SEARCH("CSE",A95)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="52" priority="63" operator="containsText" text="vacant">
       <formula>NOT(ISERROR(SEARCH("vacant",A95)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="53" priority="65" operator="containsText" text="CSE">
-      <formula>NOT(ISERROR(SEARCH("CSE",A95)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="52" priority="62" operator="containsText" text="CSE">
-      <formula>NOT(ISERROR(SEARCH("CSE",A95)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="51" priority="61" operator="containsText" text="RSE">
+    <cfRule type="containsText" dxfId="51" priority="64" operator="containsText" text="RSE">
       <formula>NOT(ISERROR(SEARCH("RSE",A95)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="50" priority="64" operator="containsText" text="RSE">
-      <formula>NOT(ISERROR(SEARCH("RSE",A95)))</formula>
+    <cfRule type="containsText" dxfId="50" priority="65" operator="containsText" text="CSE">
+      <formula>NOT(ISERROR(SEARCH("CSE",A95)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A96:A99">
@@ -19721,11 +27468,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A97">
-    <cfRule type="containsText" dxfId="47" priority="27" operator="containsText" text="CSE">
+    <cfRule type="containsText" dxfId="47" priority="26" operator="containsText" text="RSE">
+      <formula>NOT(ISERROR(SEARCH("RSE",A97)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="46" priority="27" operator="containsText" text="CSE">
       <formula>NOT(ISERROR(SEARCH("CSE",A97)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="46" priority="26" operator="containsText" text="RSE">
-      <formula>NOT(ISERROR(SEARCH("RSE",A97)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A97:A100">
@@ -19734,17 +27481,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A100">
-    <cfRule type="containsText" dxfId="44" priority="85" operator="containsText" text="CSE">
-      <formula>NOT(ISERROR(SEARCH("CSE",A100)))</formula>
+    <cfRule type="containsText" dxfId="44" priority="4" operator="containsText" text="RSE">
+      <formula>NOT(ISERROR(SEARCH("RSE",A100)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="43" priority="5" operator="containsText" text="CSE">
       <formula>NOT(ISERROR(SEARCH("CSE",A100)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="42" priority="4" operator="containsText" text="RSE">
+    <cfRule type="containsText" dxfId="42" priority="84" operator="containsText" text="RSE">
       <formula>NOT(ISERROR(SEARCH("RSE",A100)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="41" priority="84" operator="containsText" text="RSE">
-      <formula>NOT(ISERROR(SEARCH("RSE",A100)))</formula>
+    <cfRule type="containsText" dxfId="41" priority="85" operator="containsText" text="CSE">
+      <formula>NOT(ISERROR(SEARCH("CSE",A100)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A101">
@@ -19767,14 +27514,14 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A104">
-    <cfRule type="containsText" dxfId="35" priority="115" operator="containsText" text="CSE">
-      <formula>NOT(ISERROR(SEARCH("CSE",A104)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="34" priority="113" operator="containsText" text="vacant">
+    <cfRule type="containsText" dxfId="35" priority="113" operator="containsText" text="vacant">
       <formula>NOT(ISERROR(SEARCH("vacant",A104)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="33" priority="114" operator="containsText" text="RSE">
+    <cfRule type="containsText" dxfId="34" priority="114" operator="containsText" text="RSE">
       <formula>NOT(ISERROR(SEARCH("RSE",A104)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="33" priority="115" operator="containsText" text="CSE">
+      <formula>NOT(ISERROR(SEARCH("CSE",A104)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A104:A105">
@@ -19817,14 +27564,14 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A109">
-    <cfRule type="containsText" dxfId="23" priority="98" operator="containsText" text="RSE">
+    <cfRule type="containsText" dxfId="23" priority="83" operator="containsText" text="VACANT">
+      <formula>NOT(ISERROR(SEARCH("VACANT",A109)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="22" priority="98" operator="containsText" text="RSE">
       <formula>NOT(ISERROR(SEARCH("RSE",A109)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="22" priority="99" operator="containsText" text="CSE">
+    <cfRule type="containsText" dxfId="21" priority="99" operator="containsText" text="CSE">
       <formula>NOT(ISERROR(SEARCH("CSE",A109)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="21" priority="83" operator="containsText" text="VACANT">
-      <formula>NOT(ISERROR(SEARCH("VACANT",A109)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A109:A114">
@@ -19838,25 +27585,25 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A115">
-    <cfRule type="containsText" dxfId="18" priority="70" operator="containsText" text="proses">
-      <formula>NOT(ISERROR(SEARCH("proses",A115)))</formula>
+    <cfRule type="containsText" dxfId="18" priority="66" operator="containsText" text="NEED SUBMIT">
+      <formula>NOT(ISERROR(SEARCH("NEED SUBMIT",A115)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="17" priority="68" operator="containsText" text="CSE">
+    <cfRule type="containsText" dxfId="17" priority="67" operator="containsText" text="RSE">
+      <formula>NOT(ISERROR(SEARCH("RSE",A115)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="16" priority="68" operator="containsText" text="CSE">
       <formula>NOT(ISERROR(SEARCH("CSE",A115)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="16" priority="67" operator="containsText" text="RSE">
-      <formula>NOT(ISERROR(SEARCH("RSE",A115)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="15" priority="66" operator="containsText" text="NEED SUBMIT">
-      <formula>NOT(ISERROR(SEARCH("NEED SUBMIT",A115)))</formula>
+    <cfRule type="containsText" dxfId="15" priority="70" operator="containsText" text="proses">
+      <formula>NOT(ISERROR(SEARCH("proses",A115)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A116">
-    <cfRule type="containsText" dxfId="14" priority="19" operator="containsText" text="CSE">
+    <cfRule type="containsText" dxfId="14" priority="18" operator="containsText" text="RSE">
+      <formula>NOT(ISERROR(SEARCH("RSE",A116)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="13" priority="19" operator="containsText" text="CSE">
       <formula>NOT(ISERROR(SEARCH("CSE",A116)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="13" priority="18" operator="containsText" text="RSE">
-      <formula>NOT(ISERROR(SEARCH("RSE",A116)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A116:A118">
@@ -19882,25 +27629,25 @@
     <cfRule type="containsText" dxfId="7" priority="10" operator="containsText" text="RSE">
       <formula>NOT(ISERROR(SEARCH("RSE",A121)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="6" priority="12" operator="containsText" text="proses">
+    <cfRule type="containsText" dxfId="6" priority="11" operator="containsText" text="CSE">
+      <formula>NOT(ISERROR(SEARCH("CSE",A121)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="5" priority="12" operator="containsText" text="proses">
       <formula>NOT(ISERROR(SEARCH("proses",A121)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="5" priority="11" operator="containsText" text="CSE">
-      <formula>NOT(ISERROR(SEARCH("CSE",A121)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A122">
-    <cfRule type="containsText" dxfId="4" priority="91" operator="containsText" text="proses">
-      <formula>NOT(ISERROR(SEARCH("proses",A122)))</formula>
+    <cfRule type="containsText" dxfId="4" priority="13" operator="containsText" text="VACANT">
+      <formula>NOT(ISERROR(SEARCH("VACANT",A122)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="3" priority="14" operator="containsText" text="RSE">
       <formula>NOT(ISERROR(SEARCH("RSE",A122)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="2" priority="13" operator="containsText" text="VACANT">
-      <formula>NOT(ISERROR(SEARCH("VACANT",A122)))</formula>
+    <cfRule type="containsText" dxfId="2" priority="15" operator="containsText" text="CSE">
+      <formula>NOT(ISERROR(SEARCH("CSE",A122)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="1" priority="15" operator="containsText" text="CSE">
-      <formula>NOT(ISERROR(SEARCH("CSE",A122)))</formula>
+    <cfRule type="containsText" dxfId="1" priority="91" operator="containsText" text="proses">
+      <formula>NOT(ISERROR(SEARCH("proses",A122)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:D1">
